--- a/Ivestis2.xlsx
+++ b/Ivestis2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="Šios_darbaknygės" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agentura2020-my.sharepoint.com/personal/sigitas_cekanauskas_gamta_lt/Documents/Dokumentai/STACIONARUS ORO TARSOS SALTINIAI/2026-03-12 Skaiciuokles KD, GR/2026-03-12 Skaiciuokles KD, GR 2 linijos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agentura2020.sharepoint.com/sites/VidurioLietuvosaplinkostyrimuskyrius/Bendrai naudojami dokumentai/EB7-014 Darbuotojų failai/Tomo/Python 3.14.3/Skaiciavimai/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{A643DED9-AFCA-45B4-88D7-0278F4B57F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FBEC764-D3B5-4E6C-B35A-438B078D31B3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="821" firstSheet="1" activeTab="1" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="3" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Compatibility Report" sheetId="4" state="hidden" r:id="rId1"/>
@@ -2558,6 +2558,129 @@
     <xf numFmtId="164" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -2642,6 +2765,15 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2658,6 +2790,29 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="169" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2690,168 +2845,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="4" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3162,16 +3162,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ABD58BE-2006-42BB-8F0B-A2F613982E7B}">
   <sheetPr codeName="Lapas1"/>
   <dimension ref="B1:E10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.140625" customWidth="1"/>
-    <col min="2" max="2" width="64.42578125" customWidth="1"/>
-    <col min="3" max="3" width="1.5703125" customWidth="1"/>
-    <col min="4" max="4" width="5.5703125" customWidth="1"/>
+    <col min="1" max="1" width="1.1796875" customWidth="1"/>
+    <col min="2" max="2" width="64.453125" customWidth="1"/>
+    <col min="3" max="3" width="1.54296875" customWidth="1"/>
+    <col min="4" max="4" width="5.54296875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:5" ht="13" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3179,7 +3179,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5" ht="13" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3187,13 +3187,13 @@
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="2:5" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3201,13 +3201,13 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" ht="13" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -3217,13 +3217,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="2:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" ht="38" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
@@ -3233,13 +3233,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="6"/>
@@ -3254,61 +3254,61 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B3F6816-A3F5-4347-BE94-F213DC59E543}">
   <dimension ref="A3:AB31"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="144" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="144" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="144" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="144" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="144" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="144" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" style="144" customWidth="1"/>
-    <col min="8" max="12" width="9.140625" style="144"/>
-    <col min="13" max="13" width="11.140625" style="144" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="144" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="144"/>
-    <col min="16" max="16" width="10.5703125" style="144" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" style="144" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="144"/>
-    <col min="19" max="19" width="11.28515625" style="144" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" style="144" customWidth="1"/>
+    <col min="1" max="1" width="11.26953125" style="144" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" style="144" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" style="144" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="144" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" style="144" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" style="144" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" style="144" customWidth="1"/>
+    <col min="8" max="12" width="9.1796875" style="144"/>
+    <col min="13" max="13" width="11.1796875" style="144" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" style="144" customWidth="1"/>
+    <col min="15" max="15" width="9.1796875" style="144"/>
+    <col min="16" max="16" width="10.54296875" style="144" customWidth="1"/>
+    <col min="17" max="17" width="9.54296875" style="144" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.1796875" style="144"/>
+    <col min="19" max="19" width="11.26953125" style="144" customWidth="1"/>
+    <col min="20" max="20" width="11.7265625" style="144" customWidth="1"/>
     <col min="21" max="21" width="10" style="144" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" style="144" customWidth="1"/>
-    <col min="23" max="23" width="11.42578125" style="144" customWidth="1"/>
-    <col min="24" max="24" width="10.28515625" style="144" customWidth="1"/>
-    <col min="25" max="25" width="9.5703125" style="144" customWidth="1"/>
-    <col min="26" max="26" width="9.85546875" style="144" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="144"/>
+    <col min="22" max="22" width="11.7265625" style="144" customWidth="1"/>
+    <col min="23" max="23" width="11.453125" style="144" customWidth="1"/>
+    <col min="24" max="24" width="10.26953125" style="144" customWidth="1"/>
+    <col min="25" max="25" width="9.54296875" style="144" customWidth="1"/>
+    <col min="26" max="26" width="9.81640625" style="144" customWidth="1"/>
+    <col min="27" max="16384" width="9.1796875" style="144"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="D3" s="217" t="s">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="D3" s="258" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="217"/>
-      <c r="G3" s="217"/>
-      <c r="H3" s="217"/>
-      <c r="I3" s="217"/>
-      <c r="J3" s="217"/>
-      <c r="K3" s="217"/>
-      <c r="L3" s="217"/>
-      <c r="M3" s="217"/>
-      <c r="N3" s="217"/>
-      <c r="O3" s="217"/>
-      <c r="P3" s="217"/>
-      <c r="Q3" s="217"/>
-      <c r="R3" s="217"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="217"/>
-      <c r="U3" s="217"/>
-      <c r="V3" s="217"/>
-      <c r="W3" s="217"/>
-      <c r="X3" s="217"/>
-      <c r="Y3" s="217"/>
-      <c r="Z3" s="217"/>
-    </row>
-    <row r="5" spans="1:28" s="10" customFormat="1" ht="150" x14ac:dyDescent="0.2">
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="258"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
+      <c r="M3" s="258"/>
+      <c r="N3" s="258"/>
+      <c r="O3" s="258"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
+    </row>
+    <row r="5" spans="1:28" s="10" customFormat="1" ht="126" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -3394,14 +3394,14 @@
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="218">
+    <row r="6" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="259">
         <v>46210</v>
       </c>
-      <c r="B6" s="219">
+      <c r="B6" s="260">
         <v>7</v>
       </c>
-      <c r="C6" s="220" t="s">
+      <c r="C6" s="261" t="s">
         <v>140</v>
       </c>
       <c r="D6" s="151">
@@ -3492,14 +3492,14 @@
         <f>Aerodinamika!G31</f>
         <v>1.2973599999999996</v>
       </c>
-      <c r="AB6" s="215" t="s">
+      <c r="AB6" s="256" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A7" s="219"/>
-      <c r="B7" s="219"/>
-      <c r="C7" s="220"/>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="260"/>
+      <c r="B7" s="260"/>
+      <c r="C7" s="261"/>
       <c r="D7" s="151">
         <v>2</v>
       </c>
@@ -3584,12 +3584,12 @@
         <f>O6*X7</f>
         <v>0.33485669081573011</v>
       </c>
-      <c r="AB7" s="216"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="219"/>
-      <c r="B8" s="219"/>
-      <c r="C8" s="220"/>
+      <c r="AB7" s="257"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="260"/>
+      <c r="B8" s="260"/>
+      <c r="C8" s="261"/>
       <c r="D8" s="173">
         <v>3</v>
       </c>
@@ -3639,10 +3639,10 @@
       <c r="R8" s="180"/>
       <c r="S8" s="180"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" s="219"/>
-      <c r="B9" s="219"/>
-      <c r="C9" s="220"/>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="260"/>
+      <c r="B9" s="260"/>
+      <c r="C9" s="261"/>
       <c r="D9" s="151">
         <v>4</v>
       </c>
@@ -3696,10 +3696,10 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A10" s="219"/>
-      <c r="B10" s="219"/>
-      <c r="C10" s="220"/>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="260"/>
+      <c r="B10" s="260"/>
+      <c r="C10" s="261"/>
       <c r="D10" s="151">
         <v>5</v>
       </c>
@@ -3742,10 +3742,10 @@
         <v>4.1898181061790636</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A11" s="219"/>
-      <c r="B11" s="219"/>
-      <c r="C11" s="220"/>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="260"/>
+      <c r="B11" s="260"/>
+      <c r="C11" s="261"/>
       <c r="D11" s="151">
         <v>6</v>
       </c>
@@ -3788,10 +3788,10 @@
         <v>4.1898181061790636</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A12" s="219"/>
-      <c r="B12" s="219"/>
-      <c r="C12" s="220"/>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="260"/>
+      <c r="B12" s="260"/>
+      <c r="C12" s="261"/>
       <c r="D12" s="151">
         <v>7</v>
       </c>
@@ -3834,10 +3834,10 @@
         <v>4.1898181061790636</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A13" s="219"/>
-      <c r="B13" s="219"/>
-      <c r="C13" s="220"/>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="260"/>
+      <c r="B13" s="260"/>
+      <c r="C13" s="261"/>
       <c r="D13" s="151">
         <v>8</v>
       </c>
@@ -3881,10 +3881,10 @@
       </c>
       <c r="O13" s="145"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A14" s="219"/>
-      <c r="B14" s="219"/>
-      <c r="C14" s="220"/>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="260"/>
+      <c r="B14" s="260"/>
+      <c r="C14" s="261"/>
       <c r="D14" s="151">
         <v>9</v>
       </c>
@@ -3931,7 +3931,7 @@
       <c r="T14" s="39"/>
       <c r="U14" s="39"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="150"/>
       <c r="B15" s="150"/>
       <c r="C15" s="150"/>
@@ -3953,27 +3953,27 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="184"/>
       <c r="B16" s="184"/>
       <c r="C16" s="184"/>
       <c r="D16" s="173" t="s">
         <v>136</v>
       </c>
-      <c r="E16" s="221" t="s">
+      <c r="E16" s="262" t="s">
         <v>137</v>
       </c>
-      <c r="F16" s="222"/>
-      <c r="G16" s="222"/>
-      <c r="H16" s="222"/>
-      <c r="I16" s="222"/>
-      <c r="J16" s="222"/>
-      <c r="K16" s="222"/>
-      <c r="L16" s="222"/>
-      <c r="M16" s="222"/>
-      <c r="N16" s="223"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="F16" s="263"/>
+      <c r="G16" s="263"/>
+      <c r="H16" s="263"/>
+      <c r="I16" s="263"/>
+      <c r="J16" s="263"/>
+      <c r="K16" s="263"/>
+      <c r="L16" s="263"/>
+      <c r="M16" s="263"/>
+      <c r="N16" s="264"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="150"/>
       <c r="B17" s="150"/>
       <c r="C17" s="150"/>
@@ -3982,7 +3982,7 @@
       <c r="G17" s="186"/>
       <c r="N17" s="187"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="150"/>
       <c r="B18" s="150"/>
       <c r="C18" s="150"/>
@@ -3994,7 +3994,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="150"/>
       <c r="B19" s="150"/>
       <c r="C19" s="150"/>
@@ -4002,37 +4002,37 @@
       <c r="F19" s="39"/>
       <c r="N19" s="187"/>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="184"/>
       <c r="B20" s="184"/>
       <c r="C20" s="184"/>
-      <c r="D20" s="224" t="s">
+      <c r="D20" s="265" t="s">
         <v>139</v>
       </c>
-      <c r="E20" s="217"/>
-      <c r="F20" s="217"/>
-      <c r="G20" s="217"/>
-      <c r="H20" s="217"/>
-      <c r="I20" s="217"/>
-      <c r="J20" s="217"/>
-      <c r="K20" s="217"/>
-      <c r="L20" s="217"/>
-      <c r="M20" s="217"/>
-      <c r="N20" s="217"/>
-      <c r="O20" s="217"/>
-      <c r="P20" s="217"/>
-      <c r="Q20" s="217"/>
-      <c r="R20" s="217"/>
-      <c r="S20" s="217"/>
-      <c r="T20" s="217"/>
-      <c r="U20" s="217"/>
-      <c r="V20" s="217"/>
-      <c r="W20" s="217"/>
-      <c r="X20" s="217"/>
-      <c r="Y20" s="217"/>
-      <c r="Z20" s="217"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="E20" s="258"/>
+      <c r="F20" s="258"/>
+      <c r="G20" s="258"/>
+      <c r="H20" s="258"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="258"/>
+      <c r="K20" s="258"/>
+      <c r="L20" s="258"/>
+      <c r="M20" s="258"/>
+      <c r="N20" s="258"/>
+      <c r="O20" s="258"/>
+      <c r="P20" s="258"/>
+      <c r="Q20" s="258"/>
+      <c r="R20" s="258"/>
+      <c r="S20" s="258"/>
+      <c r="T20" s="258"/>
+      <c r="U20" s="258"/>
+      <c r="V20" s="258"/>
+      <c r="W20" s="258"/>
+      <c r="X20" s="258"/>
+      <c r="Y20" s="258"/>
+      <c r="Z20" s="258"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="150"/>
       <c r="B21" s="150"/>
       <c r="C21" s="150"/>
@@ -4049,7 +4049,7 @@
       <c r="N21" s="190"/>
       <c r="O21" s="188"/>
     </row>
-    <row r="22" spans="1:28" s="10" customFormat="1" ht="150" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" s="10" customFormat="1" ht="126" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>8</v>
       </c>
@@ -4135,10 +4135,10 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="225"/>
-      <c r="B23" s="225"/>
-      <c r="C23" s="225"/>
+    <row r="23" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="266"/>
+      <c r="B23" s="266"/>
+      <c r="C23" s="266"/>
       <c r="D23" s="151">
         <v>3</v>
       </c>
@@ -4215,12 +4215,12 @@
       <c r="AA23" s="165">
         <v>1.35</v>
       </c>
-      <c r="AB23" s="215"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A24" s="226"/>
-      <c r="B24" s="226"/>
-      <c r="C24" s="226"/>
+      <c r="AB23" s="256"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" s="267"/>
+      <c r="B24" s="267"/>
+      <c r="C24" s="267"/>
       <c r="D24" s="151">
         <v>15</v>
       </c>
@@ -4291,12 +4291,12 @@
         <f>O23*X24</f>
         <v>1.0498709847610572</v>
       </c>
-      <c r="AB24" s="216"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A25" s="226"/>
-      <c r="B25" s="226"/>
-      <c r="C25" s="226"/>
+      <c r="AB24" s="257"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" s="267"/>
+      <c r="B25" s="267"/>
+      <c r="C25" s="267"/>
       <c r="D25" s="173">
         <v>27</v>
       </c>
@@ -4334,10 +4334,10 @@
       <c r="R25" s="180"/>
       <c r="S25" s="180"/>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A26" s="226"/>
-      <c r="B26" s="226"/>
-      <c r="C26" s="226"/>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" s="267"/>
+      <c r="B26" s="267"/>
+      <c r="C26" s="267"/>
       <c r="D26" s="151">
         <v>4</v>
       </c>
@@ -4379,10 +4379,10 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A27" s="226"/>
-      <c r="B27" s="226"/>
-      <c r="C27" s="226"/>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" s="267"/>
+      <c r="B27" s="267"/>
+      <c r="C27" s="267"/>
       <c r="D27" s="151">
         <v>5</v>
       </c>
@@ -4413,10 +4413,10 @@
         <v>11.973560791885415</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A28" s="226"/>
-      <c r="B28" s="226"/>
-      <c r="C28" s="226"/>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="267"/>
+      <c r="B28" s="267"/>
+      <c r="C28" s="267"/>
       <c r="D28" s="151">
         <v>6</v>
       </c>
@@ -4447,10 +4447,10 @@
         <v>12.445937737064785</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A29" s="226"/>
-      <c r="B29" s="226"/>
-      <c r="C29" s="226"/>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="267"/>
+      <c r="B29" s="267"/>
+      <c r="C29" s="267"/>
       <c r="D29" s="151">
         <v>7</v>
       </c>
@@ -4481,10 +4481,10 @@
         <v>12.110405929817222</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A30" s="226"/>
-      <c r="B30" s="226"/>
-      <c r="C30" s="226"/>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" s="267"/>
+      <c r="B30" s="267"/>
+      <c r="C30" s="267"/>
       <c r="D30" s="151">
         <v>8</v>
       </c>
@@ -4516,10 +4516,10 @@
       </c>
       <c r="O30" s="145"/>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A31" s="227"/>
-      <c r="B31" s="227"/>
-      <c r="C31" s="227"/>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" s="268"/>
+      <c r="B31" s="268"/>
+      <c r="C31" s="268"/>
       <c r="D31" s="151">
         <v>9</v>
       </c>
@@ -4576,21 +4576,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B782CE6F-4AAF-42E1-A4E9-B039A4011BD6}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="40" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="40" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="40"/>
-    <col min="5" max="5" width="10.7109375" style="40" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="40"/>
-    <col min="7" max="7" width="11.28515625" style="40" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" style="40" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="40" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" style="40" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="40"/>
+    <col min="1" max="1" width="12.453125" style="40" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="40" customWidth="1"/>
+    <col min="3" max="4" width="9.1796875" style="40"/>
+    <col min="5" max="5" width="10.7265625" style="40" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="40"/>
+    <col min="7" max="7" width="11.26953125" style="40" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" style="40" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" style="40" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" style="40" customWidth="1"/>
+    <col min="11" max="16384" width="9.1796875" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A1" s="39"/>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -4601,7 +4601,7 @@
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="41"/>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -4612,21 +4612,21 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="228" t="s">
+    <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="269" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="228"/>
-      <c r="C3" s="228"/>
-      <c r="D3" s="228"/>
-      <c r="E3" s="228"/>
-      <c r="F3" s="228"/>
-      <c r="G3" s="228"/>
-      <c r="H3" s="228"/>
-      <c r="I3" s="228"/>
-      <c r="J3" s="228"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="B3" s="269"/>
+      <c r="C3" s="269"/>
+      <c r="D3" s="269"/>
+      <c r="E3" s="269"/>
+      <c r="F3" s="269"/>
+      <c r="G3" s="269"/>
+      <c r="H3" s="269"/>
+      <c r="I3" s="269"/>
+      <c r="J3" s="269"/>
+    </row>
+    <row r="4" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -4637,7 +4637,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:12" ht="90" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="84" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
         <v>38</v>
@@ -4673,7 +4673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="42"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -4687,7 +4687,7 @@
       <c r="K6" s="47"/>
       <c r="L6" s="47"/>
     </row>
-    <row r="7" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="42" t="s">
         <v>26</v>
       </c>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="L7" s="47"/>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="83"/>
       <c r="C8" s="84"/>
@@ -4742,7 +4742,7 @@
       <c r="K8" s="47"/>
       <c r="L8" s="47"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="83"/>
       <c r="C9" s="84"/>
@@ -4756,7 +4756,7 @@
       <c r="K9" s="47"/>
       <c r="L9" s="47"/>
     </row>
-    <row r="10" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="88"/>
       <c r="B10" s="83"/>
       <c r="C10" s="13"/>
@@ -4770,62 +4770,62 @@
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
     </row>
-    <row r="11" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H11" s="229" t="s">
+    <row r="11" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H11" s="270" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="232" t="s">
+      <c r="I11" s="273" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H12" s="230"/>
-      <c r="I12" s="233"/>
-    </row>
-    <row r="13" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H13" s="230"/>
-      <c r="I13" s="233"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" s="230"/>
-      <c r="I14" s="233"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" s="230"/>
-      <c r="I15" s="233"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" s="230"/>
-      <c r="I16" s="233"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H17" s="230"/>
-      <c r="I17" s="233"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H18" s="231"/>
-      <c r="I18" s="233"/>
-    </row>
-    <row r="19" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I19" s="233"/>
-    </row>
-    <row r="20" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I20" s="234"/>
-    </row>
-    <row r="21" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H12" s="271"/>
+      <c r="I12" s="274"/>
+    </row>
+    <row r="13" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H13" s="271"/>
+      <c r="I13" s="274"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H14" s="271"/>
+      <c r="I14" s="274"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H15" s="271"/>
+      <c r="I15" s="274"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H16" s="271"/>
+      <c r="I16" s="274"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="271"/>
+      <c r="I17" s="274"/>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="272"/>
+      <c r="I18" s="274"/>
+    </row>
+    <row r="19" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="274"/>
+    </row>
+    <row r="20" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="275"/>
+    </row>
+    <row r="21" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I21" s="59"/>
     </row>
-    <row r="22" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="8:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="8:9" ht="14" x14ac:dyDescent="0.3">
       <c r="I23" s="58"/>
     </row>
-    <row r="24" spans="8:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="8:9" ht="14" x14ac:dyDescent="0.3">
       <c r="I24" s="58"/>
     </row>
-    <row r="25" spans="8:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="8:9" ht="14" x14ac:dyDescent="0.3">
       <c r="I25" s="58"/>
     </row>
-    <row r="26" spans="8:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="8:9" ht="14" x14ac:dyDescent="0.3">
       <c r="I26" s="58"/>
     </row>
   </sheetData>
@@ -4845,67 +4845,67 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="13.28515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="14" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" style="14" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" style="14" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="14" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" style="14" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" style="14" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" style="14" customWidth="1"/>
-    <col min="13" max="13" width="9.85546875" style="14" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="14" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="14" customWidth="1"/>
-    <col min="16" max="16" width="6.5703125" style="14" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="14" customWidth="1"/>
-    <col min="18" max="18" width="17.5703125" style="14" customWidth="1"/>
-    <col min="19" max="19" width="15.28515625" style="14" customWidth="1"/>
-    <col min="20" max="20" width="10.42578125" style="14" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" style="14" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="14" customWidth="1"/>
-    <col min="23" max="23" width="5.140625" style="14" customWidth="1"/>
-    <col min="24" max="24" width="11.7109375" style="14" customWidth="1"/>
-    <col min="25" max="25" width="10.28515625" style="14" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="14"/>
+    <col min="1" max="2" width="13.26953125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="26.1796875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="9.81640625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="14" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" style="14" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" style="14" customWidth="1"/>
+    <col min="12" max="12" width="11.81640625" style="14" customWidth="1"/>
+    <col min="13" max="13" width="9.81640625" style="14" customWidth="1"/>
+    <col min="14" max="14" width="11.7265625" style="14" customWidth="1"/>
+    <col min="15" max="15" width="12.81640625" style="14" customWidth="1"/>
+    <col min="16" max="16" width="6.54296875" style="14" customWidth="1"/>
+    <col min="17" max="17" width="7.7265625" style="14" customWidth="1"/>
+    <col min="18" max="18" width="17.54296875" style="14" customWidth="1"/>
+    <col min="19" max="19" width="15.26953125" style="14" customWidth="1"/>
+    <col min="20" max="20" width="10.453125" style="14" customWidth="1"/>
+    <col min="21" max="21" width="11.1796875" style="14" customWidth="1"/>
+    <col min="22" max="22" width="13.453125" style="14" customWidth="1"/>
+    <col min="23" max="23" width="5.1796875" style="14" customWidth="1"/>
+    <col min="24" max="24" width="11.7265625" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.26953125" style="14" customWidth="1"/>
+    <col min="26" max="16384" width="9.1796875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+    <row r="1" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="281" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="237"/>
+      <c r="D1" s="281"/>
       <c r="E1" s="15"/>
       <c r="S1" s="16"/>
     </row>
-    <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="238" t="s">
+    <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="282" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="238"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="238"/>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="M2" s="238"/>
-      <c r="N2" s="238"/>
-      <c r="O2" s="238"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-    </row>
-    <row r="3" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="282"/>
+      <c r="C2" s="282"/>
+      <c r="D2" s="282"/>
+      <c r="E2" s="282"/>
+      <c r="F2" s="282"/>
+      <c r="G2" s="282"/>
+      <c r="H2" s="282"/>
+      <c r="I2" s="282"/>
+      <c r="J2" s="282"/>
+      <c r="K2" s="282"/>
+      <c r="L2" s="282"/>
+      <c r="M2" s="282"/>
+      <c r="N2" s="282"/>
+      <c r="O2" s="282"/>
+      <c r="P2" s="282"/>
+      <c r="Q2" s="282"/>
+      <c r="R2" s="282"/>
+      <c r="S2" s="282"/>
+    </row>
+    <row r="3" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="18"/>
@@ -4926,10 +4926,10 @@
       <c r="R3" s="18"/>
       <c r="S3" s="18"/>
     </row>
-    <row r="4" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="T4" s="28"/>
     </row>
-    <row r="5" spans="1:25" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>8</v>
       </c>
@@ -5003,15 +5003,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="251">
+    <row r="6" spans="1:25" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="215">
         <f>Greitis!A6</f>
         <v>46210</v>
       </c>
       <c r="B6" s="52">
         <v>1</v>
       </c>
-      <c r="C6" s="252" t="str">
+      <c r="C6" s="277" t="str">
         <f>Greitis!C6</f>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
@@ -5021,7 +5021,7 @@
       <c r="E6" s="141">
         <v>0.78500000000000003</v>
       </c>
-      <c r="F6" s="255">
+      <c r="F6" s="216">
         <f>V9</f>
         <v>40</v>
       </c>
@@ -5056,11 +5056,11 @@
       <c r="O6" s="137">
         <v>10</v>
       </c>
-      <c r="P6" s="257">
+      <c r="P6" s="218">
         <f>T9</f>
         <v>10</v>
       </c>
-      <c r="Q6" s="257">
+      <c r="Q6" s="218">
         <f>U9</f>
         <v>4</v>
       </c>
@@ -5083,18 +5083,18 @@
         <f>Greitis!E6</f>
         <v>0.12</v>
       </c>
-      <c r="Y6" s="257">
+      <c r="Y6" s="218">
         <f>Aerodinamika!K6</f>
         <v>1.1194047409830277</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="37"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="253"/>
+      <c r="C7" s="278"/>
       <c r="D7" s="19"/>
       <c r="E7" s="20"/>
-      <c r="F7" s="255">
+      <c r="F7" s="216">
         <f t="shared" ref="F7:H7" si="0">(F6)</f>
         <v>40</v>
       </c>
@@ -5102,18 +5102,18 @@
         <f>Greitis!G7*129*(SQRT(X7*(273+F7)/(H7+I7)/Greitis!L7))</f>
         <v>3.8790178170915426</v>
       </c>
-      <c r="H7" s="256">
+      <c r="H7" s="217">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I7" s="257">
+      <c r="I7" s="218">
         <f t="shared" ref="I7" si="1">(I6)</f>
         <v>-1</v>
       </c>
       <c r="J7" s="137">
         <v>100</v>
       </c>
-      <c r="K7" s="255">
+      <c r="K7" s="216">
         <f t="shared" ref="K7:M7" si="2">(K6)</f>
         <v>7</v>
       </c>
@@ -5121,7 +5121,7 @@
         <f>M7*N7/1000</f>
         <v>0.05</v>
       </c>
-      <c r="M7" s="256">
+      <c r="M7" s="217">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
@@ -5131,11 +5131,11 @@
       <c r="O7" s="137">
         <v>10</v>
       </c>
-      <c r="P7" s="257">
+      <c r="P7" s="218">
         <f t="shared" ref="P7" si="3">(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q7" s="257">
+      <c r="Q7" s="218">
         <f t="shared" ref="Q7" si="4">(Q6)</f>
         <v>4</v>
       </c>
@@ -5154,18 +5154,18 @@
         <f>Greitis!E7</f>
         <v>0.12</v>
       </c>
-      <c r="Y7" s="257">
+      <c r="Y7" s="218">
         <f>Aerodinamika!K7</f>
         <v>1.1194047409830277</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="37"/>
       <c r="B8" s="34"/>
-      <c r="C8" s="253"/>
+      <c r="C8" s="278"/>
       <c r="D8" s="19"/>
       <c r="E8" s="20"/>
-      <c r="F8" s="255">
+      <c r="F8" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5173,18 +5173,18 @@
         <f>Greitis!G8*129*(SQRT(X8*(273+F8)/(H8+I8)/Greitis!L8))</f>
         <v>3.8790178170915426</v>
       </c>
-      <c r="H8" s="256">
+      <c r="H8" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I8" s="257">
+      <c r="I8" s="218">
         <f t="shared" ref="I8:K8" si="5">(I6)</f>
         <v>-1</v>
       </c>
       <c r="J8" s="137">
         <v>100</v>
       </c>
-      <c r="K8" s="255">
+      <c r="K8" s="216">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
@@ -5192,7 +5192,7 @@
         <f>M8*N8/1000</f>
         <v>0.05</v>
       </c>
-      <c r="M8" s="256">
+      <c r="M8" s="217">
         <f t="shared" ref="M8" si="6">(M6)</f>
         <v>5</v>
       </c>
@@ -5202,11 +5202,11 @@
       <c r="O8" s="137">
         <v>10</v>
       </c>
-      <c r="P8" s="257">
+      <c r="P8" s="218">
         <f t="shared" ref="P8:Q8" si="7">(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q8" s="257">
+      <c r="Q8" s="218">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
@@ -5225,18 +5225,18 @@
         <f>Greitis!E8</f>
         <v>0.12</v>
       </c>
-      <c r="Y8" s="257">
+      <c r="Y8" s="218">
         <f>Aerodinamika!K8</f>
         <v>1.1194047409830277</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="51"/>
       <c r="B9" s="51"/>
-      <c r="C9" s="253"/>
+      <c r="C9" s="278"/>
       <c r="D9" s="51"/>
       <c r="E9" s="51"/>
-      <c r="F9" s="255">
+      <c r="F9" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5244,18 +5244,18 @@
         <f>Greitis!G9*129*(SQRT(X9*(273+F9)/(H9+I9)/Greitis!L9))</f>
         <v>3.8790178170915426</v>
       </c>
-      <c r="H9" s="256">
+      <c r="H9" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I9" s="257">
+      <c r="I9" s="218">
         <f t="shared" ref="I9:K9" si="8">(I6)</f>
         <v>-1</v>
       </c>
       <c r="J9" s="137">
         <v>100</v>
       </c>
-      <c r="K9" s="255">
+      <c r="K9" s="216">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
@@ -5263,7 +5263,7 @@
         <f t="shared" ref="L9:L14" si="9">M9*N9/1000</f>
         <v>0.05</v>
       </c>
-      <c r="M9" s="256">
+      <c r="M9" s="217">
         <f t="shared" ref="M9" si="10">(M6)</f>
         <v>5</v>
       </c>
@@ -5273,11 +5273,11 @@
       <c r="O9" s="137">
         <v>10</v>
       </c>
-      <c r="P9" s="257">
+      <c r="P9" s="218">
         <f t="shared" ref="P9:Q9" si="11">(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q9" s="257">
+      <c r="Q9" s="218">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -5299,18 +5299,18 @@
         <f>Greitis!E9</f>
         <v>0.12</v>
       </c>
-      <c r="Y9" s="257">
+      <c r="Y9" s="218">
         <f>Aerodinamika!K9</f>
         <v>1.1194047409830277</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="51"/>
       <c r="B10" s="51"/>
-      <c r="C10" s="253"/>
+      <c r="C10" s="278"/>
       <c r="D10" s="51"/>
       <c r="E10" s="51"/>
-      <c r="F10" s="255">
+      <c r="F10" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5318,18 +5318,18 @@
         <f>Greitis!G10*129*(SQRT(X10*(273+F10)/(H10+I10)/Greitis!L10))</f>
         <v>3.8790178170915426</v>
       </c>
-      <c r="H10" s="256">
+      <c r="H10" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I10" s="257">
+      <c r="I10" s="218">
         <f t="shared" ref="I10:K10" si="12">(I6)</f>
         <v>-1</v>
       </c>
       <c r="J10" s="137">
         <v>100</v>
       </c>
-      <c r="K10" s="255">
+      <c r="K10" s="216">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
@@ -5337,7 +5337,7 @@
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
-      <c r="M10" s="256">
+      <c r="M10" s="217">
         <f t="shared" ref="M10" si="13">(M6)</f>
         <v>5</v>
       </c>
@@ -5347,41 +5347,41 @@
       <c r="O10" s="137">
         <v>10</v>
       </c>
-      <c r="P10" s="257">
+      <c r="P10" s="218">
         <f t="shared" ref="P10:Q10" si="14">(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q10" s="257">
+      <c r="Q10" s="218">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="R10" s="51"/>
       <c r="S10" s="51"/>
-      <c r="T10" s="236" t="s">
+      <c r="T10" s="280" t="s">
         <v>33</v>
       </c>
-      <c r="U10" s="236" t="s">
+      <c r="U10" s="280" t="s">
         <v>34</v>
       </c>
-      <c r="V10" s="235" t="s">
+      <c r="V10" s="276" t="s">
         <v>41</v>
       </c>
       <c r="X10" s="211">
         <f>Greitis!E10</f>
         <v>0.12</v>
       </c>
-      <c r="Y10" s="257">
+      <c r="Y10" s="218">
         <f>Aerodinamika!K10</f>
         <v>1.1194047409830277</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="51"/>
       <c r="B11" s="51"/>
-      <c r="C11" s="253"/>
+      <c r="C11" s="278"/>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
-      <c r="F11" s="255">
+      <c r="F11" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5389,18 +5389,18 @@
         <f>Greitis!G11*129*(SQRT(X11*(273+F11)/(H11+I11)/Greitis!L11))</f>
         <v>3.8790178170915426</v>
       </c>
-      <c r="H11" s="256">
+      <c r="H11" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I11" s="257">
+      <c r="I11" s="218">
         <f t="shared" ref="I11:K11" si="15">(I6)</f>
         <v>-1</v>
       </c>
       <c r="J11" s="137">
         <v>100</v>
       </c>
-      <c r="K11" s="255">
+      <c r="K11" s="216">
         <f t="shared" si="15"/>
         <v>7</v>
       </c>
@@ -5408,7 +5408,7 @@
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
-      <c r="M11" s="256">
+      <c r="M11" s="217">
         <f t="shared" ref="M11" si="16">(M6)</f>
         <v>5</v>
       </c>
@@ -5418,35 +5418,35 @@
       <c r="O11" s="137">
         <v>10</v>
       </c>
-      <c r="P11" s="257">
+      <c r="P11" s="218">
         <f t="shared" ref="P11:Q11" si="17">(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q11" s="257">
+      <c r="Q11" s="218">
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-      <c r="T11" s="236"/>
-      <c r="U11" s="236"/>
-      <c r="V11" s="235"/>
+      <c r="T11" s="280"/>
+      <c r="U11" s="280"/>
+      <c r="V11" s="276"/>
       <c r="X11" s="211">
         <f>Greitis!E11</f>
         <v>0.12</v>
       </c>
-      <c r="Y11" s="257">
+      <c r="Y11" s="218">
         <f>Aerodinamika!K11</f>
         <v>1.1194047409830277</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="51"/>
       <c r="B12" s="51"/>
-      <c r="C12" s="253"/>
+      <c r="C12" s="278"/>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
-      <c r="F12" s="255">
+      <c r="F12" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5454,18 +5454,18 @@
         <f>Greitis!G12*129*(SQRT(X12*(273+F12)/(H12+I12)/Greitis!L12))</f>
         <v>3.8790178170915426</v>
       </c>
-      <c r="H12" s="256">
+      <c r="H12" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I12" s="257">
+      <c r="I12" s="218">
         <f t="shared" ref="I12:K12" si="18">(I6)</f>
         <v>-1</v>
       </c>
       <c r="J12" s="137">
         <v>100</v>
       </c>
-      <c r="K12" s="255">
+      <c r="K12" s="216">
         <f t="shared" si="18"/>
         <v>7</v>
       </c>
@@ -5473,7 +5473,7 @@
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
-      <c r="M12" s="256">
+      <c r="M12" s="217">
         <f t="shared" ref="M12" si="19">(M6)</f>
         <v>5</v>
       </c>
@@ -5483,35 +5483,35 @@
       <c r="O12" s="137">
         <v>10</v>
       </c>
-      <c r="P12" s="257">
+      <c r="P12" s="218">
         <f t="shared" ref="P12:Q12" si="20">(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q12" s="257">
+      <c r="Q12" s="218">
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="R12" s="51"/>
       <c r="S12" s="51"/>
-      <c r="T12" s="236"/>
-      <c r="U12" s="236"/>
-      <c r="V12" s="235"/>
+      <c r="T12" s="280"/>
+      <c r="U12" s="280"/>
+      <c r="V12" s="276"/>
       <c r="X12" s="211">
         <f>Greitis!E12</f>
         <v>0.12</v>
       </c>
-      <c r="Y12" s="257">
+      <c r="Y12" s="218">
         <f>Aerodinamika!K12</f>
         <v>1.1194047409830277</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="51"/>
       <c r="B13" s="51"/>
-      <c r="C13" s="253"/>
+      <c r="C13" s="278"/>
       <c r="D13" s="51"/>
       <c r="E13" s="51"/>
-      <c r="F13" s="255">
+      <c r="F13" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5519,18 +5519,18 @@
         <f>Greitis!G13*129*(SQRT(X13*(273+F13)/(H13+I13)/Greitis!L13))</f>
         <v>3.8790178170915426</v>
       </c>
-      <c r="H13" s="256">
+      <c r="H13" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I13" s="257">
+      <c r="I13" s="218">
         <f t="shared" ref="I13:K13" si="21">(I6)</f>
         <v>-1</v>
       </c>
       <c r="J13" s="137">
         <v>100</v>
       </c>
-      <c r="K13" s="255">
+      <c r="K13" s="216">
         <f t="shared" si="21"/>
         <v>7</v>
       </c>
@@ -5538,7 +5538,7 @@
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
-      <c r="M13" s="256">
+      <c r="M13" s="217">
         <f t="shared" ref="M13" si="22">(M6)</f>
         <v>5</v>
       </c>
@@ -5548,11 +5548,11 @@
       <c r="O13" s="137">
         <v>10</v>
       </c>
-      <c r="P13" s="257">
+      <c r="P13" s="218">
         <f t="shared" ref="P13:Q13" si="23">(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q13" s="257">
+      <c r="Q13" s="218">
         <f t="shared" si="23"/>
         <v>4</v>
       </c>
@@ -5562,18 +5562,18 @@
         <f>Greitis!E13</f>
         <v>0.12</v>
       </c>
-      <c r="Y13" s="257">
+      <c r="Y13" s="218">
         <f>Aerodinamika!K13</f>
         <v>1.1194047409830277</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="36"/>
       <c r="B14" s="36"/>
-      <c r="C14" s="254"/>
+      <c r="C14" s="279"/>
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
-      <c r="F14" s="255">
+      <c r="F14" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5581,18 +5581,18 @@
         <f>Greitis!G14*129*(SQRT(X14*(273+F14)/(H14+I14)/Greitis!L14))</f>
         <v>3.8790178170915426</v>
       </c>
-      <c r="H14" s="256">
+      <c r="H14" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I14" s="257">
+      <c r="I14" s="218">
         <f t="shared" ref="I14:K14" si="24">(I6)</f>
         <v>-1</v>
       </c>
       <c r="J14" s="137">
         <v>100</v>
       </c>
-      <c r="K14" s="255">
+      <c r="K14" s="216">
         <f t="shared" si="24"/>
         <v>7</v>
       </c>
@@ -5600,7 +5600,7 @@
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
-      <c r="M14" s="256">
+      <c r="M14" s="217">
         <f t="shared" ref="M14" si="25">(M6)</f>
         <v>5</v>
       </c>
@@ -5610,11 +5610,11 @@
       <c r="O14" s="137">
         <v>10</v>
       </c>
-      <c r="P14" s="257">
+      <c r="P14" s="218">
         <f t="shared" ref="P14:Q14" si="26">(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q14" s="257">
+      <c r="Q14" s="218">
         <f t="shared" si="26"/>
         <v>4</v>
       </c>
@@ -5624,12 +5624,12 @@
         <f>Greitis!E14</f>
         <v>0.12</v>
       </c>
-      <c r="Y14" s="257">
+      <c r="Y14" s="218">
         <f>Aerodinamika!K14</f>
         <v>1.1194047409830277</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="L15" s="72">
         <f>SUM(L6:L14)</f>
         <v>0.44999999999999996</v>
@@ -5643,7 +5643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L16" s="70" t="s">
         <v>30</v>
       </c>
@@ -5654,33 +5654,33 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="251">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A19" s="215">
         <f t="shared" ref="A19:I19" si="27">(A6)</f>
         <v>46210</v>
       </c>
-      <c r="B19" s="258">
+      <c r="B19" s="219">
         <f t="shared" si="27"/>
         <v>1</v>
       </c>
-      <c r="C19" s="252" t="str">
+      <c r="C19" s="277" t="str">
         <f t="shared" si="27"/>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
-      <c r="D19" s="259">
+      <c r="D19" s="220">
         <f t="shared" si="27"/>
         <v>1</v>
       </c>
-      <c r="E19" s="260">
+      <c r="E19" s="221">
         <f t="shared" si="27"/>
         <v>0.78500000000000003</v>
       </c>
-      <c r="F19" s="255">
+      <c r="F19" s="216">
         <f t="shared" si="27"/>
         <v>40</v>
       </c>
@@ -5688,18 +5688,18 @@
         <f>Greitis!G6*129*(SQRT(X19*(273+F19)/(H19+I19)/Greitis!L6))</f>
         <v>4.1898181061790636</v>
       </c>
-      <c r="H19" s="256">
+      <c r="H19" s="217">
         <f t="shared" si="27"/>
         <v>1000</v>
       </c>
-      <c r="I19" s="257">
+      <c r="I19" s="218">
         <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="J19" s="137">
         <v>100</v>
       </c>
-      <c r="K19" s="255">
+      <c r="K19" s="216">
         <f>(K6)</f>
         <v>7</v>
       </c>
@@ -5707,7 +5707,7 @@
         <f>M19*N19/1000</f>
         <v>0.05</v>
       </c>
-      <c r="M19" s="256">
+      <c r="M19" s="217">
         <f>(M6)</f>
         <v>5</v>
       </c>
@@ -5717,15 +5717,15 @@
       <c r="O19" s="137">
         <v>10</v>
       </c>
-      <c r="P19" s="257">
+      <c r="P19" s="218">
         <f>(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q19" s="257">
+      <c r="Q19" s="218">
         <f>(Q6)</f>
         <v>4</v>
       </c>
-      <c r="R19" s="251" t="str">
+      <c r="R19" s="215" t="str">
         <f>(R6)</f>
         <v>S.Č., 2025-05-02</v>
       </c>
@@ -5736,18 +5736,18 @@
         <f>Greitis!F6</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Y19" s="257">
+      <c r="Y19" s="218">
         <f>Aerodinamika!K19</f>
         <v>1.0363674089827735</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="37"/>
       <c r="B20" s="34"/>
-      <c r="C20" s="253"/>
+      <c r="C20" s="278"/>
       <c r="D20" s="19"/>
       <c r="E20" s="20"/>
-      <c r="F20" s="255">
+      <c r="F20" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5755,18 +5755,18 @@
         <f>Greitis!G7*129*(SQRT(X20*(273+F20)/(H20+I20)/Greitis!L7))</f>
         <v>4.1898181061790636</v>
       </c>
-      <c r="H20" s="256">
+      <c r="H20" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I20" s="257">
+      <c r="I20" s="218">
         <f>(I6)</f>
         <v>-1</v>
       </c>
       <c r="J20" s="137">
         <v>100</v>
       </c>
-      <c r="K20" s="255">
+      <c r="K20" s="216">
         <f>(K19)</f>
         <v>7</v>
       </c>
@@ -5774,7 +5774,7 @@
         <f>M20*N20/1000</f>
         <v>0.05</v>
       </c>
-      <c r="M20" s="256">
+      <c r="M20" s="217">
         <f>(M6)</f>
         <v>5</v>
       </c>
@@ -5784,11 +5784,11 @@
       <c r="O20" s="137">
         <v>10</v>
       </c>
-      <c r="P20" s="257">
+      <c r="P20" s="218">
         <f>(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q20" s="257">
+      <c r="Q20" s="218">
         <f>(Q6)</f>
         <v>4</v>
       </c>
@@ -5798,18 +5798,18 @@
         <f>Greitis!F7</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Y20" s="257">
+      <c r="Y20" s="218">
         <f>Aerodinamika!K20</f>
         <v>1.0363674089827735</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="37"/>
       <c r="B21" s="34"/>
-      <c r="C21" s="253"/>
+      <c r="C21" s="278"/>
       <c r="D21" s="19"/>
       <c r="E21" s="20"/>
-      <c r="F21" s="255">
+      <c r="F21" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5817,18 +5817,18 @@
         <f>Greitis!G8*129*(SQRT(X21*(273+F21)/(H21+I21)/Greitis!L8))</f>
         <v>4.1898181061790636</v>
       </c>
-      <c r="H21" s="256">
+      <c r="H21" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I21" s="257">
+      <c r="I21" s="218">
         <f>(I6)</f>
         <v>-1</v>
       </c>
       <c r="J21" s="137">
         <v>100</v>
       </c>
-      <c r="K21" s="255">
+      <c r="K21" s="216">
         <f>(K19)</f>
         <v>7</v>
       </c>
@@ -5836,7 +5836,7 @@
         <f>M21*N21/1000</f>
         <v>0.05</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="217">
         <f>(M6)</f>
         <v>5</v>
       </c>
@@ -5846,11 +5846,11 @@
       <c r="O21" s="137">
         <v>10</v>
       </c>
-      <c r="P21" s="257">
+      <c r="P21" s="218">
         <f>(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q21" s="257">
+      <c r="Q21" s="218">
         <f>(Q6)</f>
         <v>4</v>
       </c>
@@ -5860,18 +5860,18 @@
         <f>Greitis!F8</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Y21" s="257">
+      <c r="Y21" s="218">
         <f>Aerodinamika!K21</f>
         <v>1.0363674089827735</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="51"/>
       <c r="B22" s="51"/>
-      <c r="C22" s="253"/>
+      <c r="C22" s="278"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
-      <c r="F22" s="255">
+      <c r="F22" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5879,18 +5879,18 @@
         <f>Greitis!G9*129*(SQRT(X22*(273+F22)/(H22+I22)/Greitis!L9))</f>
         <v>4.1898181061790636</v>
       </c>
-      <c r="H22" s="256">
+      <c r="H22" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I22" s="257">
+      <c r="I22" s="218">
         <f>(I6)</f>
         <v>-1</v>
       </c>
       <c r="J22" s="137">
         <v>100</v>
       </c>
-      <c r="K22" s="255">
+      <c r="K22" s="216">
         <f>(K19)</f>
         <v>7</v>
       </c>
@@ -5898,7 +5898,7 @@
         <f t="shared" ref="L22:L27" si="28">M22*N22/1000</f>
         <v>0.05</v>
       </c>
-      <c r="M22" s="256">
+      <c r="M22" s="217">
         <f>(M6)</f>
         <v>5</v>
       </c>
@@ -5908,11 +5908,11 @@
       <c r="O22" s="137">
         <v>10</v>
       </c>
-      <c r="P22" s="257">
+      <c r="P22" s="218">
         <f>(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q22" s="257">
+      <c r="Q22" s="218">
         <f>(Q6)</f>
         <v>4</v>
       </c>
@@ -5922,18 +5922,18 @@
         <f>Greitis!F9</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Y22" s="257">
+      <c r="Y22" s="218">
         <f>Aerodinamika!K22</f>
         <v>1.0363674089827735</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="51"/>
       <c r="B23" s="51"/>
-      <c r="C23" s="253"/>
+      <c r="C23" s="278"/>
       <c r="D23" s="51"/>
       <c r="E23" s="51"/>
-      <c r="F23" s="255">
+      <c r="F23" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -5941,18 +5941,18 @@
         <f>Greitis!G10*129*(SQRT(X23*(273+F23)/(H23+I23)/Greitis!L10))</f>
         <v>4.1898181061790636</v>
       </c>
-      <c r="H23" s="256">
+      <c r="H23" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I23" s="257">
+      <c r="I23" s="218">
         <f>(I6)</f>
         <v>-1</v>
       </c>
       <c r="J23" s="137">
         <v>100</v>
       </c>
-      <c r="K23" s="255">
+      <c r="K23" s="216">
         <f>(K19)</f>
         <v>7</v>
       </c>
@@ -5960,7 +5960,7 @@
         <f t="shared" si="28"/>
         <v>0.05</v>
       </c>
-      <c r="M23" s="256">
+      <c r="M23" s="217">
         <f>(M6)</f>
         <v>5</v>
       </c>
@@ -5970,11 +5970,11 @@
       <c r="O23" s="137">
         <v>10</v>
       </c>
-      <c r="P23" s="257">
+      <c r="P23" s="218">
         <f>(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q23" s="257">
+      <c r="Q23" s="218">
         <f>(Q6)</f>
         <v>4</v>
       </c>
@@ -5984,18 +5984,18 @@
         <f>Greitis!F10</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Y23" s="257">
+      <c r="Y23" s="218">
         <f>Aerodinamika!K23</f>
         <v>1.0363674089827735</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="51"/>
       <c r="B24" s="51"/>
-      <c r="C24" s="253"/>
+      <c r="C24" s="278"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
-      <c r="F24" s="255">
+      <c r="F24" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -6003,18 +6003,18 @@
         <f>Greitis!G11*129*(SQRT(X24*(273+F24)/(H24+I24)/Greitis!L11))</f>
         <v>4.1898181061790636</v>
       </c>
-      <c r="H24" s="256">
+      <c r="H24" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I24" s="257">
+      <c r="I24" s="218">
         <f>(I6)</f>
         <v>-1</v>
       </c>
       <c r="J24" s="137">
         <v>100</v>
       </c>
-      <c r="K24" s="255">
+      <c r="K24" s="216">
         <f>(K19)</f>
         <v>7</v>
       </c>
@@ -6022,7 +6022,7 @@
         <f t="shared" si="28"/>
         <v>0.05</v>
       </c>
-      <c r="M24" s="256">
+      <c r="M24" s="217">
         <f>(M6)</f>
         <v>5</v>
       </c>
@@ -6032,11 +6032,11 @@
       <c r="O24" s="137">
         <v>10</v>
       </c>
-      <c r="P24" s="257">
+      <c r="P24" s="218">
         <f>(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q24" s="257">
+      <c r="Q24" s="218">
         <f>(Q6)</f>
         <v>4</v>
       </c>
@@ -6046,18 +6046,18 @@
         <f>Greitis!F11</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Y24" s="257">
+      <c r="Y24" s="218">
         <f>Aerodinamika!K24</f>
         <v>1.0363674089827735</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="51"/>
       <c r="B25" s="51"/>
-      <c r="C25" s="253"/>
+      <c r="C25" s="278"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
-      <c r="F25" s="255">
+      <c r="F25" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -6065,18 +6065,18 @@
         <f>Greitis!G12*129*(SQRT(X25*(273+F25)/(H25+I25)/Greitis!L12))</f>
         <v>4.1898181061790636</v>
       </c>
-      <c r="H25" s="256">
+      <c r="H25" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I25" s="257">
+      <c r="I25" s="218">
         <f>(I6)</f>
         <v>-1</v>
       </c>
       <c r="J25" s="137">
         <v>100</v>
       </c>
-      <c r="K25" s="255">
+      <c r="K25" s="216">
         <f>(K19)</f>
         <v>7</v>
       </c>
@@ -6084,7 +6084,7 @@
         <f t="shared" si="28"/>
         <v>0.05</v>
       </c>
-      <c r="M25" s="256">
+      <c r="M25" s="217">
         <f>(M6)</f>
         <v>5</v>
       </c>
@@ -6094,11 +6094,11 @@
       <c r="O25" s="137">
         <v>10</v>
       </c>
-      <c r="P25" s="257">
+      <c r="P25" s="218">
         <f>(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q25" s="257">
+      <c r="Q25" s="218">
         <f>(Q6)</f>
         <v>4</v>
       </c>
@@ -6108,18 +6108,18 @@
         <f>Greitis!F12</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Y25" s="257">
+      <c r="Y25" s="218">
         <f>Aerodinamika!K25</f>
         <v>1.0363674089827735</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="51"/>
       <c r="B26" s="51"/>
-      <c r="C26" s="253"/>
+      <c r="C26" s="278"/>
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
-      <c r="F26" s="255">
+      <c r="F26" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -6127,18 +6127,18 @@
         <f>Greitis!G13*129*(SQRT(X26*(273+F26)/(H26+I26)/Greitis!L13))</f>
         <v>4.1898181061790636</v>
       </c>
-      <c r="H26" s="256">
+      <c r="H26" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I26" s="257">
+      <c r="I26" s="218">
         <f>(I6)</f>
         <v>-1</v>
       </c>
       <c r="J26" s="137">
         <v>100</v>
       </c>
-      <c r="K26" s="255">
+      <c r="K26" s="216">
         <f>(K19)</f>
         <v>7</v>
       </c>
@@ -6146,7 +6146,7 @@
         <f t="shared" si="28"/>
         <v>0.05</v>
       </c>
-      <c r="M26" s="256">
+      <c r="M26" s="217">
         <f>(M6)</f>
         <v>5</v>
       </c>
@@ -6156,11 +6156,11 @@
       <c r="O26" s="137">
         <v>10</v>
       </c>
-      <c r="P26" s="257">
+      <c r="P26" s="218">
         <f>(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q26" s="257">
+      <c r="Q26" s="218">
         <f>(Q6)</f>
         <v>4</v>
       </c>
@@ -6170,18 +6170,18 @@
         <f>Greitis!F13</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Y26" s="257">
+      <c r="Y26" s="218">
         <f>Aerodinamika!K26</f>
         <v>1.0363674089827735</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="36"/>
       <c r="B27" s="36"/>
-      <c r="C27" s="254"/>
+      <c r="C27" s="279"/>
       <c r="D27" s="36"/>
       <c r="E27" s="36"/>
-      <c r="F27" s="255">
+      <c r="F27" s="216">
         <f>(F6)</f>
         <v>40</v>
       </c>
@@ -6189,18 +6189,18 @@
         <f>Greitis!G14*129*(SQRT(X27*(273+F27)/(H27+I27)/Greitis!L14))</f>
         <v>4.1898181061790636</v>
       </c>
-      <c r="H27" s="256">
+      <c r="H27" s="217">
         <f>(H6)</f>
         <v>1000</v>
       </c>
-      <c r="I27" s="257">
+      <c r="I27" s="218">
         <f>(I6)</f>
         <v>-1</v>
       </c>
       <c r="J27" s="137">
         <v>100</v>
       </c>
-      <c r="K27" s="255">
+      <c r="K27" s="216">
         <f>(K19)</f>
         <v>7</v>
       </c>
@@ -6208,7 +6208,7 @@
         <f t="shared" si="28"/>
         <v>0.05</v>
       </c>
-      <c r="M27" s="256">
+      <c r="M27" s="217">
         <f>(M6)</f>
         <v>5</v>
       </c>
@@ -6218,11 +6218,11 @@
       <c r="O27" s="137">
         <v>10</v>
       </c>
-      <c r="P27" s="257">
+      <c r="P27" s="218">
         <f t="shared" ref="P27:Q27" si="29">(P6)</f>
         <v>10</v>
       </c>
-      <c r="Q27" s="257">
+      <c r="Q27" s="218">
         <f t="shared" si="29"/>
         <v>4</v>
       </c>
@@ -6232,12 +6232,12 @@
         <f>Greitis!F14</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Y27" s="257">
+      <c r="Y27" s="218">
         <f>Aerodinamika!K27</f>
         <v>1.0363674089827735</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="L28" s="72">
         <f>SUM(L19:L27)</f>
         <v>0.44999999999999996</v>
@@ -6251,7 +6251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="28" x14ac:dyDescent="0.3">
       <c r="L29" s="70" t="s">
         <v>30</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L31" s="69"/>
       <c r="M31" s="127">
         <f>(M15+M28)</f>
@@ -6276,7 +6276,7 @@
       <c r="P31" s="99"/>
       <c r="Q31" s="99"/>
     </row>
-    <row r="32" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L32" s="69"/>
       <c r="M32" s="49" t="s">
         <v>100</v>
@@ -6285,20 +6285,20 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="25"/>
       <c r="B78" s="25"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="25"/>
       <c r="B79" s="25"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="25"/>
       <c r="B80" s="25"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="25"/>
       <c r="B81" s="25"/>
     </row>
@@ -6329,55 +6329,55 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q263"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="14" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="14" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="14" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" style="14" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="11.26953125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="16.7265625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" style="14" customWidth="1" outlineLevel="1"/>
     <col min="10" max="10" width="10" style="14" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="10.28515625" style="14" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="14" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="14" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" style="14" customWidth="1"/>
     <col min="13" max="13" width="17" style="14" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="14" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="14"/>
+    <col min="14" max="14" width="14.81640625" style="14" customWidth="1"/>
+    <col min="15" max="16384" width="9.1796875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+    <row r="1" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="281" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="237"/>
+      <c r="D1" s="281"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="239" t="s">
+    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="283" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
-      <c r="M2" s="239"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="283"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
+      <c r="I2" s="283"/>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="283"/>
+      <c r="M2" s="283"/>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="24"/>
       <c r="H3" s="25"/>
       <c r="Q3" s="16"/>
     </row>
-    <row r="4" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:17" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:17" ht="126.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="102" t="s">
         <v>8</v>
       </c>
@@ -6421,20 +6421,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="261">
+    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="222">
         <f>Paėmimas!A6</f>
         <v>46210</v>
       </c>
-      <c r="B6" s="262">
+      <c r="B6" s="223">
         <f>Paėmimas!B6</f>
         <v>1</v>
       </c>
-      <c r="C6" s="252" t="str">
+      <c r="C6" s="277" t="str">
         <f>Paėmimas!C6</f>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
-      <c r="D6" s="263">
+      <c r="D6" s="224">
         <f>Paėmimas!L6</f>
         <v>0.05</v>
       </c>
@@ -6450,7 +6450,7 @@
         <f>((Paėmimas!Q6/100)*1.965)+((Paėmimas!P6/100)*1.429)+((1-(Paėmimas!Q6/100)-(Paėmimas!P6/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H6" s="263">
+      <c r="H6" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6470,20 +6470,20 @@
         <f>AVERAGE(K6:K14)</f>
         <v>1.1194047409830274</v>
       </c>
-      <c r="M6" s="264" t="str">
+      <c r="M6" s="225" t="str">
         <f>Paėmimas!R6</f>
         <v>S.Č., 2025-05-02</v>
       </c>
-      <c r="N6" s="265" t="str">
+      <c r="N6" s="226" t="str">
         <f>Paėmimas!S6</f>
         <v>1 linija, 1 filtras</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="61"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="253"/>
-      <c r="D7" s="263">
+      <c r="C7" s="278"/>
+      <c r="D7" s="224">
         <f>Paėmimas!L7</f>
         <v>0.05</v>
       </c>
@@ -6496,7 +6496,7 @@
         <f>((Paėmimas!Q7/100)*1.965)+((Paėmimas!P7/100)*1.429)+((1-(Paėmimas!Q7/100)-(Paėmimas!P7/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H7" s="263">
+      <c r="H7" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6516,11 +6516,11 @@
       <c r="M7" s="62"/>
       <c r="N7" s="34"/>
     </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="61"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="253"/>
-      <c r="D8" s="263">
+      <c r="C8" s="278"/>
+      <c r="D8" s="224">
         <f>Paėmimas!L8</f>
         <v>0.05</v>
       </c>
@@ -6533,7 +6533,7 @@
         <f>((Paėmimas!Q8/100)*1.965)+((Paėmimas!P8/100)*1.429)+((1-(Paėmimas!Q8/100)-(Paėmimas!P8/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H8" s="263">
+      <c r="H8" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6553,11 +6553,11 @@
       <c r="M8" s="62"/>
       <c r="N8" s="34"/>
     </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="61"/>
       <c r="B9" s="23"/>
-      <c r="C9" s="253"/>
-      <c r="D9" s="263">
+      <c r="C9" s="278"/>
+      <c r="D9" s="224">
         <f>Paėmimas!L9</f>
         <v>0.05</v>
       </c>
@@ -6570,7 +6570,7 @@
         <f>((Paėmimas!Q9/100)*1.965)+((Paėmimas!P9/100)*1.429)+((1-(Paėmimas!Q9/100)-(Paėmimas!P9/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H9" s="263">
+      <c r="H9" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6590,11 +6590,11 @@
       <c r="M9" s="62"/>
       <c r="N9" s="34"/>
     </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="253"/>
-      <c r="D10" s="263">
+      <c r="C10" s="278"/>
+      <c r="D10" s="224">
         <f>Paėmimas!L10</f>
         <v>0.05</v>
       </c>
@@ -6607,7 +6607,7 @@
         <f>((Paėmimas!Q10/100)*1.965)+((Paėmimas!P10/100)*1.429)+((1-(Paėmimas!Q10/100)-(Paėmimas!P10/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H10" s="263">
+      <c r="H10" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6627,11 +6627,11 @@
       <c r="M10" s="62"/>
       <c r="N10" s="34"/>
     </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="61"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="253"/>
-      <c r="D11" s="263">
+      <c r="C11" s="278"/>
+      <c r="D11" s="224">
         <f>Paėmimas!L11</f>
         <v>0.05</v>
       </c>
@@ -6644,7 +6644,7 @@
         <f>((Paėmimas!Q11/100)*1.965)+((Paėmimas!P11/100)*1.429)+((1-(Paėmimas!Q11/100)-(Paėmimas!P11/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H11" s="263">
+      <c r="H11" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6664,11 +6664,11 @@
       <c r="M11" s="62"/>
       <c r="N11" s="34"/>
     </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="61"/>
       <c r="B12" s="23"/>
-      <c r="C12" s="253"/>
-      <c r="D12" s="263">
+      <c r="C12" s="278"/>
+      <c r="D12" s="224">
         <f>Paėmimas!L12</f>
         <v>0.05</v>
       </c>
@@ -6681,7 +6681,7 @@
         <f>((Paėmimas!Q12/100)*1.965)+((Paėmimas!P12/100)*1.429)+((1-(Paėmimas!Q12/100)-(Paėmimas!P12/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H12" s="263">
+      <c r="H12" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6701,11 +6701,11 @@
       <c r="M12" s="62"/>
       <c r="N12" s="34"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="61"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="253"/>
-      <c r="D13" s="263">
+      <c r="C13" s="278"/>
+      <c r="D13" s="224">
         <f>Paėmimas!L13</f>
         <v>0.05</v>
       </c>
@@ -6718,7 +6718,7 @@
         <f>((Paėmimas!Q13/100)*1.965)+((Paėmimas!P13/100)*1.429)+((1-(Paėmimas!Q13/100)-(Paėmimas!P13/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H13" s="263">
+      <c r="H13" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6738,11 +6738,11 @@
       <c r="M13" s="62"/>
       <c r="N13" s="34"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="63"/>
       <c r="B14" s="64"/>
-      <c r="C14" s="254"/>
-      <c r="D14" s="263">
+      <c r="C14" s="279"/>
+      <c r="D14" s="224">
         <f>Paėmimas!L14</f>
         <v>0.05</v>
       </c>
@@ -6755,7 +6755,7 @@
         <f>((Paėmimas!Q14/100)*1.965)+((Paėmimas!P14/100)*1.429)+((1-(Paėmimas!Q14/100)-(Paėmimas!P14/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H14" s="263">
+      <c r="H14" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6775,7 +6775,7 @@
       <c r="M14" s="65"/>
       <c r="N14" s="22"/>
     </row>
-    <row r="15" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="80"/>
       <c r="D15" s="80"/>
       <c r="E15" s="80"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="J15" s="80"/>
     </row>
-    <row r="16" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="81"/>
       <c r="D16" s="81"/>
       <c r="E16" s="81"/>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="J16" s="81"/>
     </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="81"/>
       <c r="D17" s="81"/>
       <c r="E17" s="81"/>
@@ -6815,20 +6815,20 @@
       <c r="I17" s="81"/>
       <c r="J17" s="81"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="261">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="222">
         <f>Paėmimas!A19</f>
         <v>46210</v>
       </c>
-      <c r="B19" s="262">
+      <c r="B19" s="223">
         <f>Paėmimas!B19</f>
         <v>1</v>
       </c>
-      <c r="C19" s="252" t="str">
+      <c r="C19" s="277" t="str">
         <f>Paėmimas!C19</f>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
-      <c r="D19" s="263">
+      <c r="D19" s="224">
         <f>Paėmimas!L19</f>
         <v>0.05</v>
       </c>
@@ -6844,7 +6844,7 @@
         <f>((Paėmimas!Q19/100)*1.965)+((Paėmimas!P19/100)*1.429)+((1-(Paėmimas!Q19/100)-(Paėmimas!P19/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H19" s="263">
+      <c r="H19" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6864,20 +6864,20 @@
         <f>AVERAGE(K19:K27)</f>
         <v>1.0363674089827735</v>
       </c>
-      <c r="M19" s="264" t="str">
+      <c r="M19" s="225" t="str">
         <f>Paėmimas!R19</f>
         <v>S.Č., 2025-05-02</v>
       </c>
-      <c r="N19" s="265" t="str">
+      <c r="N19" s="226" t="str">
         <f>Paėmimas!S19</f>
         <v>2 linija, 2 filtras</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="61"/>
       <c r="B20" s="23"/>
-      <c r="C20" s="253"/>
-      <c r="D20" s="263">
+      <c r="C20" s="278"/>
+      <c r="D20" s="224">
         <f>Paėmimas!L20</f>
         <v>0.05</v>
       </c>
@@ -6890,7 +6890,7 @@
         <f>((Paėmimas!Q20/100)*1.965)+((Paėmimas!P20/100)*1.429)+((1-(Paėmimas!Q20/100)-(Paėmimas!P20/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H20" s="263">
+      <c r="H20" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6910,11 +6910,11 @@
       <c r="M20" s="62"/>
       <c r="N20" s="34"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="61"/>
       <c r="B21" s="23"/>
-      <c r="C21" s="253"/>
-      <c r="D21" s="263">
+      <c r="C21" s="278"/>
+      <c r="D21" s="224">
         <f>Paėmimas!L21</f>
         <v>0.05</v>
       </c>
@@ -6927,7 +6927,7 @@
         <f>((Paėmimas!Q21/100)*1.965)+((Paėmimas!P21/100)*1.429)+((1-(Paėmimas!Q21/100)-(Paėmimas!P21/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H21" s="263">
+      <c r="H21" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6947,11 +6947,11 @@
       <c r="M21" s="62"/>
       <c r="N21" s="34"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="61"/>
       <c r="B22" s="23"/>
-      <c r="C22" s="253"/>
-      <c r="D22" s="263">
+      <c r="C22" s="278"/>
+      <c r="D22" s="224">
         <f>Paėmimas!L22</f>
         <v>0.05</v>
       </c>
@@ -6964,7 +6964,7 @@
         <f>((Paėmimas!Q22/100)*1.965)+((Paėmimas!P22/100)*1.429)+((1-(Paėmimas!Q22/100)-(Paėmimas!P22/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H22" s="263">
+      <c r="H22" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -6984,11 +6984,11 @@
       <c r="M22" s="62"/>
       <c r="N22" s="34"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="61"/>
       <c r="B23" s="23"/>
-      <c r="C23" s="253"/>
-      <c r="D23" s="263">
+      <c r="C23" s="278"/>
+      <c r="D23" s="224">
         <f>Paėmimas!L23</f>
         <v>0.05</v>
       </c>
@@ -7001,7 +7001,7 @@
         <f>((Paėmimas!Q23/100)*1.965)+((Paėmimas!P23/100)*1.429)+((1-(Paėmimas!Q23/100)-(Paėmimas!P23/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H23" s="263">
+      <c r="H23" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -7021,11 +7021,11 @@
       <c r="M23" s="62"/>
       <c r="N23" s="34"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="61"/>
       <c r="B24" s="23"/>
-      <c r="C24" s="253"/>
-      <c r="D24" s="263">
+      <c r="C24" s="278"/>
+      <c r="D24" s="224">
         <f>Paėmimas!L24</f>
         <v>0.05</v>
       </c>
@@ -7038,7 +7038,7 @@
         <f>((Paėmimas!Q24/100)*1.965)+((Paėmimas!P24/100)*1.429)+((1-(Paėmimas!Q24/100)-(Paėmimas!P24/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H24" s="263">
+      <c r="H24" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -7058,11 +7058,11 @@
       <c r="M24" s="62"/>
       <c r="N24" s="34"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="61"/>
       <c r="B25" s="23"/>
-      <c r="C25" s="253"/>
-      <c r="D25" s="263">
+      <c r="C25" s="278"/>
+      <c r="D25" s="224">
         <f>Paėmimas!L25</f>
         <v>0.05</v>
       </c>
@@ -7075,7 +7075,7 @@
         <f>((Paėmimas!Q25/100)*1.965)+((Paėmimas!P25/100)*1.429)+((1-(Paėmimas!Q25/100)-(Paėmimas!P25/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H25" s="263">
+      <c r="H25" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -7095,11 +7095,11 @@
       <c r="M25" s="62"/>
       <c r="N25" s="34"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="61"/>
       <c r="B26" s="23"/>
-      <c r="C26" s="253"/>
-      <c r="D26" s="263">
+      <c r="C26" s="278"/>
+      <c r="D26" s="224">
         <f>Paėmimas!L26</f>
         <v>0.05</v>
       </c>
@@ -7112,7 +7112,7 @@
         <f>((Paėmimas!Q26/100)*1.965)+((Paėmimas!P26/100)*1.429)+((1-(Paėmimas!Q26/100)-(Paėmimas!P26/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H26" s="263">
+      <c r="H26" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -7132,11 +7132,11 @@
       <c r="M26" s="62"/>
       <c r="N26" s="34"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="63"/>
       <c r="B27" s="64"/>
-      <c r="C27" s="254"/>
-      <c r="D27" s="263">
+      <c r="C27" s="279"/>
+      <c r="D27" s="224">
         <f>Paėmimas!L27</f>
         <v>0.05</v>
       </c>
@@ -7149,7 +7149,7 @@
         <f>((Paėmimas!Q27/100)*1.965)+((Paėmimas!P27/100)*1.429)+((1-(Paėmimas!Q27/100)-(Paėmimas!P27/100))*1.251)</f>
         <v>1.2973599999999998</v>
       </c>
-      <c r="H27" s="263">
+      <c r="H27" s="224">
         <f>H2O!K7</f>
         <v>6.352173020933173</v>
       </c>
@@ -7169,7 +7169,7 @@
       <c r="M27" s="65"/>
       <c r="N27" s="22"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C28" s="80"/>
       <c r="D28" s="80"/>
       <c r="E28" s="80"/>
@@ -7192,7 +7192,7 @@
         <v>1.0778860749829005</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="56" x14ac:dyDescent="0.3">
       <c r="C29" s="81"/>
       <c r="D29" s="81"/>
       <c r="E29" s="81"/>
@@ -7211,7 +7211,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C30" s="82"/>
       <c r="D30" s="82"/>
       <c r="E30" s="82"/>
@@ -7221,7 +7221,7 @@
       <c r="I30" s="82"/>
       <c r="J30" s="82"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C31" s="82"/>
       <c r="D31" s="82"/>
       <c r="E31" s="82"/>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="J31" s="82"/>
     </row>
-    <row r="32" spans="1:14" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="82"/>
       <c r="D32" s="82"/>
       <c r="E32" s="82"/>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="J32" s="82"/>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C33" s="82"/>
       <c r="D33" s="82"/>
       <c r="E33" s="82"/>
@@ -7261,7 +7261,7 @@
       <c r="I33" s="82"/>
       <c r="J33" s="82"/>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C34" s="82"/>
       <c r="D34" s="82"/>
       <c r="E34" s="82"/>
@@ -7271,13 +7271,13 @@
       <c r="I34" s="82"/>
       <c r="J34" s="82"/>
     </row>
-    <row r="262" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C262" s="26"/>
       <c r="D262" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="263" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C263" s="27"/>
       <c r="D263" s="14" t="s">
         <v>11</v>
@@ -7307,64 +7307,64 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="14" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" style="14" customWidth="1"/>
     <col min="7" max="7" width="11" style="14" customWidth="1"/>
-    <col min="8" max="9" width="10.28515625" style="14" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" style="14" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="14" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" style="14" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="14" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" style="14" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" style="14" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="14" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" style="14"/>
-    <col min="18" max="18" width="9.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="14"/>
+    <col min="8" max="9" width="10.26953125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" style="14" customWidth="1"/>
+    <col min="11" max="11" width="14.26953125" style="14" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" style="14" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" style="14" customWidth="1"/>
+    <col min="14" max="14" width="17.7265625" style="14" customWidth="1"/>
+    <col min="15" max="15" width="8.26953125" style="14" customWidth="1"/>
+    <col min="16" max="16" width="12.7265625" style="14" customWidth="1"/>
+    <col min="17" max="17" width="9.1796875" style="14"/>
+    <col min="18" max="18" width="9.54296875" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.1796875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+    <row r="1" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="281" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="237"/>
+      <c r="D1" s="281"/>
       <c r="R1" s="16"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="239" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="283" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="239"/>
-      <c r="C2" s="239"/>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
-      <c r="M2" s="239"/>
-      <c r="N2" s="239"/>
+      <c r="B2" s="283"/>
+      <c r="C2" s="283"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="283"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
+      <c r="I2" s="283"/>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="283"/>
+      <c r="M2" s="283"/>
+      <c r="N2" s="283"/>
       <c r="O2" s="129"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="F3" s="29"/>
       <c r="L3" s="16"/>
       <c r="M3" s="16"/>
     </row>
-    <row r="4" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
     </row>
-    <row r="5" spans="1:18" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="88.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="102" t="s">
         <v>8</v>
       </c>
@@ -7414,32 +7414,32 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="266">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="227">
         <f>Paėmimas!A6</f>
         <v>46210</v>
       </c>
-      <c r="B6" s="267">
+      <c r="B6" s="228">
         <f>Svėrimas!A6</f>
         <v>1</v>
       </c>
-      <c r="C6" s="268" t="str">
+      <c r="C6" s="284" t="str">
         <f>Paėmimas!C6</f>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
-      <c r="D6" s="270">
+      <c r="D6" s="229">
         <f>Svėrimas!C6</f>
         <v>1</v>
       </c>
-      <c r="E6" s="271">
+      <c r="E6" s="230">
         <f>Svėrimas!G6</f>
         <v>4.0517000000000003</v>
       </c>
-      <c r="F6" s="272">
+      <c r="F6" s="231">
         <f>Svėrimas!L6</f>
         <v>4.0567000000000002</v>
       </c>
-      <c r="G6" s="272">
+      <c r="G6" s="231">
         <f>Svėrimas!M9</f>
         <v>1.0000000000021103E-4</v>
       </c>
@@ -7447,11 +7447,11 @@
         <f>Svėrimas!M11/O6</f>
         <v>4.9999999998107114E-5</v>
       </c>
-      <c r="I6" s="272">
+      <c r="I6" s="231">
         <f>Svėrimas!M16</f>
         <v>0</v>
       </c>
-      <c r="J6" s="275">
+      <c r="J6" s="234">
         <f>Aerodinamika!F6</f>
         <v>0.38567526745942327</v>
       </c>
@@ -7467,35 +7467,35 @@
         <f>(((F6-E6)+H6)+((F7-E7)+H7))/G6</f>
         <v>100.99999999974688</v>
       </c>
-      <c r="N6" s="277" t="str">
+      <c r="N6" s="236" t="str">
         <f>Svėrimas!N6</f>
         <v>S.Č., 2026-05-03</v>
       </c>
       <c r="O6" s="52">
         <v>2</v>
       </c>
-      <c r="P6" s="278" t="str">
+      <c r="P6" s="237" t="str">
         <f>Paėmimas!S6</f>
         <v>1 linija, 1 filtras</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="279"/>
-      <c r="B7" s="280"/>
-      <c r="C7" s="268"/>
-      <c r="D7" s="273">
+    <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="238"/>
+      <c r="B7" s="239"/>
+      <c r="C7" s="284"/>
+      <c r="D7" s="232">
         <f>Svėrimas!C7</f>
         <v>2</v>
       </c>
-      <c r="E7" s="271">
+      <c r="E7" s="230">
         <f>Svėrimas!G7</f>
         <v>4.0517000000000003</v>
       </c>
-      <c r="F7" s="274">
+      <c r="F7" s="233">
         <f>Svėrimas!L7</f>
         <v>4.0567000000000002</v>
       </c>
-      <c r="G7" s="272">
+      <c r="G7" s="231">
         <f>Svėrimas!M9</f>
         <v>1.0000000000021103E-4</v>
       </c>
@@ -7503,11 +7503,11 @@
         <f>Svėrimas!M11/O6</f>
         <v>4.9999999998107114E-5</v>
       </c>
-      <c r="I7" s="272">
+      <c r="I7" s="231">
         <f>Svėrimas!M16</f>
         <v>0</v>
       </c>
-      <c r="J7" s="276">
+      <c r="J7" s="235">
         <f>Aerodinamika!F19</f>
         <v>0.38567526745942327</v>
       </c>
@@ -7520,30 +7520,30 @@
         <v>0.2222222222226912</v>
       </c>
       <c r="M7" s="105"/>
-      <c r="N7" s="289"/>
+      <c r="N7" s="248"/>
       <c r="O7" s="34"/>
-      <c r="P7" s="278" t="str">
+      <c r="P7" s="237" t="str">
         <f>Paėmimas!S19</f>
         <v>2 linija, 2 filtras</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="281"/>
-      <c r="B8" s="282"/>
-      <c r="C8" s="269"/>
-      <c r="D8" s="283"/>
-      <c r="E8" s="284"/>
-      <c r="F8" s="285"/>
-      <c r="G8" s="285"/>
-      <c r="H8" s="285"/>
-      <c r="I8" s="285"/>
-      <c r="J8" s="286"/>
-      <c r="K8" s="287"/>
-      <c r="L8" s="288"/>
+    <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="240"/>
+      <c r="B8" s="241"/>
+      <c r="C8" s="285"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="243"/>
+      <c r="F8" s="244"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="244"/>
+      <c r="I8" s="244"/>
+      <c r="J8" s="245"/>
+      <c r="K8" s="246"/>
+      <c r="L8" s="247"/>
       <c r="M8" s="106"/>
-      <c r="N8" s="290"/>
+      <c r="N8" s="249"/>
       <c r="O8" s="22"/>
-      <c r="P8" s="291"/>
+      <c r="P8" s="250"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="ieqiJL1WxT84xM0k666oCEmNfoWReeXzs0vrOc8nReKwH1pTB8/U/pemJ1qa5tJCEy36XaGRMWCHclwNALw8Mw==" saltValue="sF01Xq3vGPf/99H6AuS/5g==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
@@ -7565,97 +7565,97 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330ECBA1-822C-4C0F-89AB-CB2C7AD5643F}">
   <dimension ref="A1:P18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" style="98" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="98" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="98" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="98" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="98" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="98" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="98" customWidth="1"/>
+    <col min="1" max="1" width="13.7265625" style="98" customWidth="1"/>
+    <col min="2" max="2" width="25.1796875" style="98" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" style="98" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" style="98" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" style="98" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" style="98" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" style="98" customWidth="1"/>
     <col min="8" max="8" width="18" style="98" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="98" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" style="98" customWidth="1"/>
+    <col min="9" max="9" width="11.26953125" style="98" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" style="98" customWidth="1"/>
     <col min="11" max="11" width="11" style="98" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" style="98" customWidth="1"/>
-    <col min="13" max="13" width="20.28515625" style="98" customWidth="1"/>
-    <col min="14" max="14" width="16.85546875" style="98" customWidth="1"/>
-    <col min="15" max="15" width="31.28515625" style="98" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="98"/>
+    <col min="12" max="12" width="11.1796875" style="98" customWidth="1"/>
+    <col min="13" max="13" width="20.26953125" style="98" customWidth="1"/>
+    <col min="14" max="14" width="16.81640625" style="98" customWidth="1"/>
+    <col min="15" max="15" width="31.26953125" style="98" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="98"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="237" t="s">
+    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="281" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="237"/>
-      <c r="E1" s="237"/>
-      <c r="F1" s="237"/>
-    </row>
-    <row r="2" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="239" t="s">
+      <c r="D1" s="281"/>
+      <c r="E1" s="281"/>
+      <c r="F1" s="281"/>
+    </row>
+    <row r="2" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="283" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="239"/>
-      <c r="C2" s="239"/>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
-      <c r="M2" s="239"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="239"/>
-    </row>
-    <row r="4" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="241" t="s">
+      <c r="B2" s="283"/>
+      <c r="C2" s="283"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="283"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
+      <c r="I2" s="283"/>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="283"/>
+      <c r="M2" s="283"/>
+      <c r="N2" s="283"/>
+      <c r="O2" s="283"/>
+    </row>
+    <row r="4" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="292" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="292" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="289" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="248" t="s">
+      <c r="D4" s="289" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="248" t="s">
+      <c r="E4" s="289" t="s">
         <v>86</v>
       </c>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248" t="s">
+      <c r="F4" s="289"/>
+      <c r="G4" s="289"/>
+      <c r="H4" s="289" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="245" t="s">
+      <c r="I4" s="296" t="s">
         <v>87</v>
       </c>
-      <c r="J4" s="240" t="s">
+      <c r="J4" s="291" t="s">
         <v>88</v>
       </c>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="M4" s="247" t="s">
+      <c r="K4" s="291"/>
+      <c r="L4" s="291"/>
+      <c r="M4" s="298" t="s">
         <v>89</v>
       </c>
-      <c r="N4" s="240" t="s">
+      <c r="N4" s="291" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="243" t="s">
+      <c r="O4" s="294" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="242"/>
-      <c r="B5" s="242"/>
-      <c r="C5" s="249"/>
-      <c r="D5" s="248"/>
+    <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="293"/>
+      <c r="B5" s="293"/>
+      <c r="C5" s="290"/>
+      <c r="D5" s="289"/>
       <c r="E5" s="120">
         <v>1</v>
       </c>
@@ -7665,8 +7665,8 @@
       <c r="G5" s="120">
         <v>3</v>
       </c>
-      <c r="H5" s="248"/>
-      <c r="I5" s="246"/>
+      <c r="H5" s="289"/>
+      <c r="I5" s="297"/>
       <c r="J5" s="12">
         <v>1</v>
       </c>
@@ -7677,22 +7677,22 @@
         <v>3</v>
       </c>
       <c r="M5" s="299"/>
-      <c r="N5" s="240"/>
-      <c r="O5" s="244"/>
-    </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="292">
+      <c r="N5" s="291"/>
+      <c r="O5" s="295"/>
+    </row>
+    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="251">
         <f>Paėmimas!B6</f>
         <v>1</v>
       </c>
-      <c r="B6" s="293" t="str">
+      <c r="B6" s="286" t="str">
         <f>Paėmimas!C6</f>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
       <c r="C6" s="94">
         <v>1</v>
       </c>
-      <c r="D6" s="296">
+      <c r="D6" s="252">
         <f>Paėmimas!A6</f>
         <v>46210</v>
       </c>
@@ -7705,7 +7705,7 @@
       <c r="G6" s="200">
         <v>4.0517000000000003</v>
       </c>
-      <c r="H6" s="297" t="str">
+      <c r="H6" s="253" t="str">
         <f>Paėmimas!R6</f>
         <v>S.Č., 2025-05-02</v>
       </c>
@@ -7728,14 +7728,14 @@
       <c r="N6" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="292" t="str">
+      <c r="O6" s="251" t="str">
         <f>Paėmimas!S6</f>
         <v>1 linija, 1 filtras</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34"/>
-      <c r="B7" s="294"/>
+      <c r="B7" s="287"/>
       <c r="C7" s="33">
         <v>2</v>
       </c>
@@ -7765,14 +7765,14 @@
         <v>4.9999999999998934E-3</v>
       </c>
       <c r="N7" s="32"/>
-      <c r="O7" s="298" t="str">
+      <c r="O7" s="254" t="str">
         <f>Paėmimas!S19</f>
         <v>2 linija, 2 filtras</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34"/>
-      <c r="B8" s="294"/>
+      <c r="B8" s="287"/>
       <c r="C8" s="33"/>
       <c r="D8" s="92"/>
       <c r="E8" s="201"/>
@@ -7788,11 +7788,11 @@
         <v>0</v>
       </c>
       <c r="N8" s="93"/>
-      <c r="O8" s="300"/>
-    </row>
-    <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="O8" s="255"/>
+    </row>
+    <row r="9" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A9" s="34"/>
-      <c r="B9" s="294"/>
+      <c r="B9" s="287"/>
       <c r="C9" s="33">
         <v>3</v>
       </c>
@@ -7827,9 +7827,9 @@
       </c>
       <c r="P9" s="100"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="34"/>
-      <c r="B10" s="294"/>
+      <c r="B10" s="287"/>
       <c r="C10" s="33"/>
       <c r="D10" s="92"/>
       <c r="E10" s="201"/>
@@ -7844,9 +7844,9 @@
       <c r="N10" s="93"/>
       <c r="O10" s="121"/>
     </row>
-    <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A11" s="34"/>
-      <c r="B11" s="294"/>
+      <c r="B11" s="287"/>
       <c r="C11" s="33">
         <v>41</v>
       </c>
@@ -7880,9 +7880,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="34"/>
-      <c r="B12" s="294"/>
+      <c r="B12" s="287"/>
       <c r="C12" s="115" t="s">
         <v>46</v>
       </c>
@@ -7916,9 +7916,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A13" s="34"/>
-      <c r="B13" s="294"/>
+      <c r="B13" s="287"/>
       <c r="C13" s="116" t="s">
         <v>47</v>
       </c>
@@ -7952,9 +7952,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A14" s="34"/>
-      <c r="B14" s="294"/>
+      <c r="B14" s="287"/>
       <c r="C14" s="116" t="s">
         <v>48</v>
       </c>
@@ -7988,9 +7988,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A15" s="34"/>
-      <c r="B15" s="294"/>
+      <c r="B15" s="287"/>
       <c r="C15" s="117" t="s">
         <v>49</v>
       </c>
@@ -8024,9 +8024,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="22"/>
-      <c r="B16" s="295"/>
+      <c r="B16" s="288"/>
       <c r="C16" s="33"/>
       <c r="D16" s="95"/>
       <c r="E16" s="21"/>
@@ -8046,10 +8046,10 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
       <c r="K17" s="99"/>
     </row>
-    <row r="18" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="11:11" x14ac:dyDescent="0.25">
       <c r="K18" s="99"/>
     </row>
   </sheetData>
@@ -8060,11 +8060,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="14">
-    <mergeCell ref="B6:B16"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:H5"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A2:O2"/>
@@ -8074,6 +8069,11 @@
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="M4:M5"/>
+    <mergeCell ref="B6:B16"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:H5"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -8090,24 +8090,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{813C0327-CFDD-498C-87C1-8E379F217A35}">
   <dimension ref="A3:D10"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" style="107" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="107" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="107" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" style="107" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="107"/>
+    <col min="1" max="1" width="14.7265625" style="107" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" style="107" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" style="107" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" style="107" customWidth="1"/>
+    <col min="5" max="16384" width="9.1796875" style="107"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="250" t="s">
+    <row r="3" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="300" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="250"/>
-      <c r="C3" s="250"/>
-      <c r="D3" s="250"/>
-    </row>
-    <row r="5" spans="1:4" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="300"/>
+      <c r="C3" s="300"/>
+      <c r="D3" s="300"/>
+    </row>
+    <row r="5" spans="1:4" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="108" t="s">
         <v>90</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="110">
         <f>(B6*C6*D6)/1000000</f>
         <v>1.944</v>
@@ -8136,7 +8136,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C10" s="114"/>
     </row>
   </sheetData>
@@ -8149,8 +8149,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="4b563907e9d350ee522af8821e27efcb">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b66428c7ca4fa35ccc5d072d5fab9d0" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
     <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
     <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
     <xsd:element name="properties">
@@ -8404,6 +8404,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
@@ -8414,35 +8423,19 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A76AEC4-30EA-47BC-874D-3E7B98533503}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AC080F3-B1ED-4875-B2A8-C621A7222607}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605DD0A7-BC00-4D8E-8AD3-26E2A9FDEA54}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
-    <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709F4DDD-DF1A-450D-8BF1-976CA47CFD58}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -8451,12 +8444,4 @@
     <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605DD0A7-BC00-4D8E-8AD3-26E2A9FDEA54}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Ivestis2.xlsx
+++ b/Ivestis2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agentura2020.sharepoint.com/sites/VidurioLietuvosaplinkostyrimuskyrius/Bendrai naudojami dokumentai/EB7-014 Darbuotojų failai/Tomo/Python 3.14.3/Skaiciavimai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{A643DED9-AFCA-45B4-88D7-0278F4B57F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FBEC764-D3B5-4E6C-B35A-438B078D31B3}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{A643DED9-AFCA-45B4-88D7-0278F4B57F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6025435-91FC-459E-B688-2967D1DEEE39}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="3" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="4" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Compatibility Report" sheetId="4" state="hidden" r:id="rId1"/>
@@ -2681,6 +2681,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -2761,31 +2786,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2796,6 +2796,42 @@
     <xf numFmtId="169" fontId="4" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2811,42 +2847,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -3253,6 +3253,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B3F6816-A3F5-4347-BE94-F213DC59E543}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A3:AB31"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3282,31 +3285,31 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="D3" s="258" t="s">
+      <c r="D3" s="265" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="258"/>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="M3" s="258"/>
-      <c r="N3" s="258"/>
-      <c r="O3" s="258"/>
-      <c r="P3" s="258"/>
-      <c r="Q3" s="258"/>
-      <c r="R3" s="258"/>
-      <c r="S3" s="258"/>
-      <c r="T3" s="258"/>
-      <c r="U3" s="258"/>
-      <c r="V3" s="258"/>
-      <c r="W3" s="258"/>
-      <c r="X3" s="258"/>
-      <c r="Y3" s="258"/>
-      <c r="Z3" s="258"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="265"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="265"/>
+      <c r="I3" s="265"/>
+      <c r="J3" s="265"/>
+      <c r="K3" s="265"/>
+      <c r="L3" s="265"/>
+      <c r="M3" s="265"/>
+      <c r="N3" s="265"/>
+      <c r="O3" s="265"/>
+      <c r="P3" s="265"/>
+      <c r="Q3" s="265"/>
+      <c r="R3" s="265"/>
+      <c r="S3" s="265"/>
+      <c r="T3" s="265"/>
+      <c r="U3" s="265"/>
+      <c r="V3" s="265"/>
+      <c r="W3" s="265"/>
+      <c r="X3" s="265"/>
+      <c r="Y3" s="265"/>
+      <c r="Z3" s="265"/>
     </row>
     <row r="5" spans="1:28" s="10" customFormat="1" ht="126" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
@@ -3395,13 +3398,13 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="259">
+      <c r="A6" s="266">
         <v>46210</v>
       </c>
-      <c r="B6" s="260">
+      <c r="B6" s="267">
         <v>7</v>
       </c>
-      <c r="C6" s="261" t="s">
+      <c r="C6" s="268" t="s">
         <v>140</v>
       </c>
       <c r="D6" s="151">
@@ -3492,14 +3495,14 @@
         <f>Aerodinamika!G31</f>
         <v>1.2973599999999996</v>
       </c>
-      <c r="AB6" s="256" t="s">
+      <c r="AB6" s="263" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="260"/>
-      <c r="B7" s="260"/>
-      <c r="C7" s="261"/>
+      <c r="A7" s="267"/>
+      <c r="B7" s="267"/>
+      <c r="C7" s="268"/>
       <c r="D7" s="151">
         <v>2</v>
       </c>
@@ -3584,12 +3587,12 @@
         <f>O6*X7</f>
         <v>0.33485669081573011</v>
       </c>
-      <c r="AB7" s="257"/>
+      <c r="AB7" s="264"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="260"/>
-      <c r="B8" s="260"/>
-      <c r="C8" s="261"/>
+      <c r="A8" s="267"/>
+      <c r="B8" s="267"/>
+      <c r="C8" s="268"/>
       <c r="D8" s="173">
         <v>3</v>
       </c>
@@ -3640,9 +3643,9 @@
       <c r="S8" s="180"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="260"/>
-      <c r="B9" s="260"/>
-      <c r="C9" s="261"/>
+      <c r="A9" s="267"/>
+      <c r="B9" s="267"/>
+      <c r="C9" s="268"/>
       <c r="D9" s="151">
         <v>4</v>
       </c>
@@ -3697,9 +3700,9 @@
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="260"/>
-      <c r="B10" s="260"/>
-      <c r="C10" s="261"/>
+      <c r="A10" s="267"/>
+      <c r="B10" s="267"/>
+      <c r="C10" s="268"/>
       <c r="D10" s="151">
         <v>5</v>
       </c>
@@ -3743,9 +3746,9 @@
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="260"/>
-      <c r="B11" s="260"/>
-      <c r="C11" s="261"/>
+      <c r="A11" s="267"/>
+      <c r="B11" s="267"/>
+      <c r="C11" s="268"/>
       <c r="D11" s="151">
         <v>6</v>
       </c>
@@ -3789,9 +3792,9 @@
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="260"/>
-      <c r="B12" s="260"/>
-      <c r="C12" s="261"/>
+      <c r="A12" s="267"/>
+      <c r="B12" s="267"/>
+      <c r="C12" s="268"/>
       <c r="D12" s="151">
         <v>7</v>
       </c>
@@ -3835,9 +3838,9 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="260"/>
-      <c r="B13" s="260"/>
-      <c r="C13" s="261"/>
+      <c r="A13" s="267"/>
+      <c r="B13" s="267"/>
+      <c r="C13" s="268"/>
       <c r="D13" s="151">
         <v>8</v>
       </c>
@@ -3882,9 +3885,9 @@
       <c r="O13" s="145"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="260"/>
-      <c r="B14" s="260"/>
-      <c r="C14" s="261"/>
+      <c r="A14" s="267"/>
+      <c r="B14" s="267"/>
+      <c r="C14" s="268"/>
       <c r="D14" s="151">
         <v>9</v>
       </c>
@@ -3960,18 +3963,18 @@
       <c r="D16" s="173" t="s">
         <v>136</v>
       </c>
-      <c r="E16" s="262" t="s">
+      <c r="E16" s="269" t="s">
         <v>137</v>
       </c>
-      <c r="F16" s="263"/>
-      <c r="G16" s="263"/>
-      <c r="H16" s="263"/>
-      <c r="I16" s="263"/>
-      <c r="J16" s="263"/>
-      <c r="K16" s="263"/>
-      <c r="L16" s="263"/>
-      <c r="M16" s="263"/>
-      <c r="N16" s="264"/>
+      <c r="F16" s="270"/>
+      <c r="G16" s="270"/>
+      <c r="H16" s="270"/>
+      <c r="I16" s="270"/>
+      <c r="J16" s="270"/>
+      <c r="K16" s="270"/>
+      <c r="L16" s="270"/>
+      <c r="M16" s="270"/>
+      <c r="N16" s="271"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="150"/>
@@ -4006,31 +4009,31 @@
       <c r="A20" s="184"/>
       <c r="B20" s="184"/>
       <c r="C20" s="184"/>
-      <c r="D20" s="265" t="s">
+      <c r="D20" s="272" t="s">
         <v>139</v>
       </c>
-      <c r="E20" s="258"/>
-      <c r="F20" s="258"/>
-      <c r="G20" s="258"/>
-      <c r="H20" s="258"/>
-      <c r="I20" s="258"/>
-      <c r="J20" s="258"/>
-      <c r="K20" s="258"/>
-      <c r="L20" s="258"/>
-      <c r="M20" s="258"/>
-      <c r="N20" s="258"/>
-      <c r="O20" s="258"/>
-      <c r="P20" s="258"/>
-      <c r="Q20" s="258"/>
-      <c r="R20" s="258"/>
-      <c r="S20" s="258"/>
-      <c r="T20" s="258"/>
-      <c r="U20" s="258"/>
-      <c r="V20" s="258"/>
-      <c r="W20" s="258"/>
-      <c r="X20" s="258"/>
-      <c r="Y20" s="258"/>
-      <c r="Z20" s="258"/>
+      <c r="E20" s="265"/>
+      <c r="F20" s="265"/>
+      <c r="G20" s="265"/>
+      <c r="H20" s="265"/>
+      <c r="I20" s="265"/>
+      <c r="J20" s="265"/>
+      <c r="K20" s="265"/>
+      <c r="L20" s="265"/>
+      <c r="M20" s="265"/>
+      <c r="N20" s="265"/>
+      <c r="O20" s="265"/>
+      <c r="P20" s="265"/>
+      <c r="Q20" s="265"/>
+      <c r="R20" s="265"/>
+      <c r="S20" s="265"/>
+      <c r="T20" s="265"/>
+      <c r="U20" s="265"/>
+      <c r="V20" s="265"/>
+      <c r="W20" s="265"/>
+      <c r="X20" s="265"/>
+      <c r="Y20" s="265"/>
+      <c r="Z20" s="265"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="150"/>
@@ -4136,9 +4139,9 @@
       </c>
     </row>
     <row r="23" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="266"/>
-      <c r="B23" s="266"/>
-      <c r="C23" s="266"/>
+      <c r="A23" s="273"/>
+      <c r="B23" s="273"/>
+      <c r="C23" s="273"/>
       <c r="D23" s="151">
         <v>3</v>
       </c>
@@ -4215,12 +4218,12 @@
       <c r="AA23" s="165">
         <v>1.35</v>
       </c>
-      <c r="AB23" s="256"/>
+      <c r="AB23" s="263"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="267"/>
-      <c r="B24" s="267"/>
-      <c r="C24" s="267"/>
+      <c r="A24" s="274"/>
+      <c r="B24" s="274"/>
+      <c r="C24" s="274"/>
       <c r="D24" s="151">
         <v>15</v>
       </c>
@@ -4291,12 +4294,12 @@
         <f>O23*X24</f>
         <v>1.0498709847610572</v>
       </c>
-      <c r="AB24" s="257"/>
+      <c r="AB24" s="264"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="267"/>
-      <c r="B25" s="267"/>
-      <c r="C25" s="267"/>
+      <c r="A25" s="274"/>
+      <c r="B25" s="274"/>
+      <c r="C25" s="274"/>
       <c r="D25" s="173">
         <v>27</v>
       </c>
@@ -4335,9 +4338,9 @@
       <c r="S25" s="180"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="267"/>
-      <c r="B26" s="267"/>
-      <c r="C26" s="267"/>
+      <c r="A26" s="274"/>
+      <c r="B26" s="274"/>
+      <c r="C26" s="274"/>
       <c r="D26" s="151">
         <v>4</v>
       </c>
@@ -4380,9 +4383,9 @@
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="267"/>
-      <c r="B27" s="267"/>
-      <c r="C27" s="267"/>
+      <c r="A27" s="274"/>
+      <c r="B27" s="274"/>
+      <c r="C27" s="274"/>
       <c r="D27" s="151">
         <v>5</v>
       </c>
@@ -4414,9 +4417,9 @@
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="267"/>
-      <c r="B28" s="267"/>
-      <c r="C28" s="267"/>
+      <c r="A28" s="274"/>
+      <c r="B28" s="274"/>
+      <c r="C28" s="274"/>
       <c r="D28" s="151">
         <v>6</v>
       </c>
@@ -4448,9 +4451,9 @@
       </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="267"/>
-      <c r="B29" s="267"/>
-      <c r="C29" s="267"/>
+      <c r="A29" s="274"/>
+      <c r="B29" s="274"/>
+      <c r="C29" s="274"/>
       <c r="D29" s="151">
         <v>7</v>
       </c>
@@ -4482,9 +4485,9 @@
       </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A30" s="267"/>
-      <c r="B30" s="267"/>
-      <c r="C30" s="267"/>
+      <c r="A30" s="274"/>
+      <c r="B30" s="274"/>
+      <c r="C30" s="274"/>
       <c r="D30" s="151">
         <v>8</v>
       </c>
@@ -4517,9 +4520,9 @@
       <c r="O30" s="145"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A31" s="268"/>
-      <c r="B31" s="268"/>
-      <c r="C31" s="268"/>
+      <c r="A31" s="275"/>
+      <c r="B31" s="275"/>
+      <c r="C31" s="275"/>
       <c r="D31" s="151">
         <v>9</v>
       </c>
@@ -4570,6 +4573,7 @@
     <mergeCell ref="C23:C31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4613,18 +4617,18 @@
       <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="269" t="s">
+      <c r="A3" s="276" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="269"/>
-      <c r="C3" s="269"/>
-      <c r="D3" s="269"/>
-      <c r="E3" s="269"/>
-      <c r="F3" s="269"/>
-      <c r="G3" s="269"/>
-      <c r="H3" s="269"/>
-      <c r="I3" s="269"/>
-      <c r="J3" s="269"/>
+      <c r="B3" s="276"/>
+      <c r="C3" s="276"/>
+      <c r="D3" s="276"/>
+      <c r="E3" s="276"/>
+      <c r="F3" s="276"/>
+      <c r="G3" s="276"/>
+      <c r="H3" s="276"/>
+      <c r="I3" s="276"/>
+      <c r="J3" s="276"/>
     </row>
     <row r="4" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
@@ -4771,46 +4775,46 @@
       <c r="L10" s="47"/>
     </row>
     <row r="11" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H11" s="270" t="s">
+      <c r="H11" s="277" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="273" t="s">
+      <c r="I11" s="280" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H12" s="271"/>
-      <c r="I12" s="274"/>
+      <c r="H12" s="278"/>
+      <c r="I12" s="281"/>
     </row>
     <row r="13" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H13" s="271"/>
-      <c r="I13" s="274"/>
+      <c r="H13" s="278"/>
+      <c r="I13" s="281"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H14" s="271"/>
-      <c r="I14" s="274"/>
+      <c r="H14" s="278"/>
+      <c r="I14" s="281"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H15" s="271"/>
-      <c r="I15" s="274"/>
+      <c r="H15" s="278"/>
+      <c r="I15" s="281"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H16" s="271"/>
-      <c r="I16" s="274"/>
+      <c r="H16" s="278"/>
+      <c r="I16" s="281"/>
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="271"/>
-      <c r="I17" s="274"/>
+      <c r="H17" s="278"/>
+      <c r="I17" s="281"/>
     </row>
     <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="272"/>
-      <c r="I18" s="274"/>
+      <c r="H18" s="279"/>
+      <c r="I18" s="281"/>
     </row>
     <row r="19" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I19" s="274"/>
+      <c r="I19" s="281"/>
     </row>
     <row r="20" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I20" s="275"/>
+      <c r="I20" s="282"/>
     </row>
     <row r="21" spans="8:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I21" s="59"/>
@@ -4836,6 +4840,7 @@
     <mergeCell ref="I11:I20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4875,35 +4880,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="281" t="s">
+      <c r="C1" s="261" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="281"/>
+      <c r="D1" s="261"/>
       <c r="E1" s="15"/>
       <c r="S1" s="16"/>
     </row>
     <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="282" t="s">
+      <c r="A2" s="262" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="282"/>
-      <c r="C2" s="282"/>
-      <c r="D2" s="282"/>
-      <c r="E2" s="282"/>
-      <c r="F2" s="282"/>
-      <c r="G2" s="282"/>
-      <c r="H2" s="282"/>
-      <c r="I2" s="282"/>
-      <c r="J2" s="282"/>
-      <c r="K2" s="282"/>
-      <c r="L2" s="282"/>
-      <c r="M2" s="282"/>
-      <c r="N2" s="282"/>
-      <c r="O2" s="282"/>
-      <c r="P2" s="282"/>
-      <c r="Q2" s="282"/>
-      <c r="R2" s="282"/>
-      <c r="S2" s="282"/>
+      <c r="B2" s="262"/>
+      <c r="C2" s="262"/>
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
+      <c r="G2" s="262"/>
+      <c r="H2" s="262"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="262"/>
+      <c r="K2" s="262"/>
+      <c r="L2" s="262"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="262"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="262"/>
     </row>
     <row r="3" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
@@ -5011,7 +5016,7 @@
       <c r="B6" s="52">
         <v>1</v>
       </c>
-      <c r="C6" s="277" t="str">
+      <c r="C6" s="257" t="str">
         <f>Greitis!C6</f>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
@@ -5091,7 +5096,7 @@
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="37"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="278"/>
+      <c r="C7" s="258"/>
       <c r="D7" s="19"/>
       <c r="E7" s="20"/>
       <c r="F7" s="216">
@@ -5162,7 +5167,7 @@
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="37"/>
       <c r="B8" s="34"/>
-      <c r="C8" s="278"/>
+      <c r="C8" s="258"/>
       <c r="D8" s="19"/>
       <c r="E8" s="20"/>
       <c r="F8" s="216">
@@ -5233,7 +5238,7 @@
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="51"/>
       <c r="B9" s="51"/>
-      <c r="C9" s="278"/>
+      <c r="C9" s="258"/>
       <c r="D9" s="51"/>
       <c r="E9" s="51"/>
       <c r="F9" s="216">
@@ -5307,7 +5312,7 @@
     <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="51"/>
       <c r="B10" s="51"/>
-      <c r="C10" s="278"/>
+      <c r="C10" s="258"/>
       <c r="D10" s="51"/>
       <c r="E10" s="51"/>
       <c r="F10" s="216">
@@ -5357,13 +5362,13 @@
       </c>
       <c r="R10" s="51"/>
       <c r="S10" s="51"/>
-      <c r="T10" s="280" t="s">
+      <c r="T10" s="260" t="s">
         <v>33</v>
       </c>
-      <c r="U10" s="280" t="s">
+      <c r="U10" s="260" t="s">
         <v>34</v>
       </c>
-      <c r="V10" s="276" t="s">
+      <c r="V10" s="256" t="s">
         <v>41</v>
       </c>
       <c r="X10" s="211">
@@ -5378,7 +5383,7 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="51"/>
       <c r="B11" s="51"/>
-      <c r="C11" s="278"/>
+      <c r="C11" s="258"/>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
       <c r="F11" s="216">
@@ -5428,9 +5433,9 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-      <c r="T11" s="280"/>
-      <c r="U11" s="280"/>
-      <c r="V11" s="276"/>
+      <c r="T11" s="260"/>
+      <c r="U11" s="260"/>
+      <c r="V11" s="256"/>
       <c r="X11" s="211">
         <f>Greitis!E11</f>
         <v>0.12</v>
@@ -5443,7 +5448,7 @@
     <row r="12" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="51"/>
       <c r="B12" s="51"/>
-      <c r="C12" s="278"/>
+      <c r="C12" s="258"/>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
       <c r="F12" s="216">
@@ -5493,9 +5498,9 @@
       </c>
       <c r="R12" s="51"/>
       <c r="S12" s="51"/>
-      <c r="T12" s="280"/>
-      <c r="U12" s="280"/>
-      <c r="V12" s="276"/>
+      <c r="T12" s="260"/>
+      <c r="U12" s="260"/>
+      <c r="V12" s="256"/>
       <c r="X12" s="211">
         <f>Greitis!E12</f>
         <v>0.12</v>
@@ -5508,7 +5513,7 @@
     <row r="13" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="51"/>
       <c r="B13" s="51"/>
-      <c r="C13" s="278"/>
+      <c r="C13" s="258"/>
       <c r="D13" s="51"/>
       <c r="E13" s="51"/>
       <c r="F13" s="216">
@@ -5570,7 +5575,7 @@
     <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="36"/>
       <c r="B14" s="36"/>
-      <c r="C14" s="279"/>
+      <c r="C14" s="259"/>
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
       <c r="F14" s="216">
@@ -5668,7 +5673,7 @@
         <f t="shared" si="27"/>
         <v>1</v>
       </c>
-      <c r="C19" s="277" t="str">
+      <c r="C19" s="257" t="str">
         <f t="shared" si="27"/>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
@@ -5744,7 +5749,7 @@
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="37"/>
       <c r="B20" s="34"/>
-      <c r="C20" s="278"/>
+      <c r="C20" s="258"/>
       <c r="D20" s="19"/>
       <c r="E20" s="20"/>
       <c r="F20" s="216">
@@ -5806,7 +5811,7 @@
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="37"/>
       <c r="B21" s="34"/>
-      <c r="C21" s="278"/>
+      <c r="C21" s="258"/>
       <c r="D21" s="19"/>
       <c r="E21" s="20"/>
       <c r="F21" s="216">
@@ -5868,7 +5873,7 @@
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="51"/>
       <c r="B22" s="51"/>
-      <c r="C22" s="278"/>
+      <c r="C22" s="258"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="216">
@@ -5930,7 +5935,7 @@
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="51"/>
       <c r="B23" s="51"/>
-      <c r="C23" s="278"/>
+      <c r="C23" s="258"/>
       <c r="D23" s="51"/>
       <c r="E23" s="51"/>
       <c r="F23" s="216">
@@ -5992,7 +5997,7 @@
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="51"/>
       <c r="B24" s="51"/>
-      <c r="C24" s="278"/>
+      <c r="C24" s="258"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
       <c r="F24" s="216">
@@ -6054,7 +6059,7 @@
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="51"/>
       <c r="B25" s="51"/>
-      <c r="C25" s="278"/>
+      <c r="C25" s="258"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
       <c r="F25" s="216">
@@ -6116,7 +6121,7 @@
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="51"/>
       <c r="B26" s="51"/>
-      <c r="C26" s="278"/>
+      <c r="C26" s="258"/>
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
       <c r="F26" s="216">
@@ -6178,7 +6183,7 @@
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="36"/>
       <c r="B27" s="36"/>
-      <c r="C27" s="279"/>
+      <c r="C27" s="259"/>
       <c r="D27" s="36"/>
       <c r="E27" s="36"/>
       <c r="F27" s="216">
@@ -6315,7 +6320,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.19685039370078741" right="0" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="66" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;CPuslapių &amp;P &amp;R&amp;"Times New Roman,Paryškintasis"E5-5_02         
 2022-02-01, EV</oddFooter>
@@ -6349,10 +6354,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="281" t="s">
+      <c r="C1" s="261" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="281"/>
+      <c r="D1" s="261"/>
       <c r="Q1" s="16"/>
     </row>
     <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6430,7 +6435,7 @@
         <f>Paėmimas!B6</f>
         <v>1</v>
       </c>
-      <c r="C6" s="277" t="str">
+      <c r="C6" s="257" t="str">
         <f>Paėmimas!C6</f>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
@@ -6482,7 +6487,7 @@
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="61"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="278"/>
+      <c r="C7" s="258"/>
       <c r="D7" s="224">
         <f>Paėmimas!L7</f>
         <v>0.05</v>
@@ -6519,7 +6524,7 @@
     <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="61"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="278"/>
+      <c r="C8" s="258"/>
       <c r="D8" s="224">
         <f>Paėmimas!L8</f>
         <v>0.05</v>
@@ -6556,7 +6561,7 @@
     <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="61"/>
       <c r="B9" s="23"/>
-      <c r="C9" s="278"/>
+      <c r="C9" s="258"/>
       <c r="D9" s="224">
         <f>Paėmimas!L9</f>
         <v>0.05</v>
@@ -6593,7 +6598,7 @@
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="278"/>
+      <c r="C10" s="258"/>
       <c r="D10" s="224">
         <f>Paėmimas!L10</f>
         <v>0.05</v>
@@ -6630,7 +6635,7 @@
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="61"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="278"/>
+      <c r="C11" s="258"/>
       <c r="D11" s="224">
         <f>Paėmimas!L11</f>
         <v>0.05</v>
@@ -6667,7 +6672,7 @@
     <row r="12" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="61"/>
       <c r="B12" s="23"/>
-      <c r="C12" s="278"/>
+      <c r="C12" s="258"/>
       <c r="D12" s="224">
         <f>Paėmimas!L12</f>
         <v>0.05</v>
@@ -6704,7 +6709,7 @@
     <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="61"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="278"/>
+      <c r="C13" s="258"/>
       <c r="D13" s="224">
         <f>Paėmimas!L13</f>
         <v>0.05</v>
@@ -6741,7 +6746,7 @@
     <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="63"/>
       <c r="B14" s="64"/>
-      <c r="C14" s="279"/>
+      <c r="C14" s="259"/>
       <c r="D14" s="224">
         <f>Paėmimas!L14</f>
         <v>0.05</v>
@@ -6824,7 +6829,7 @@
         <f>Paėmimas!B19</f>
         <v>1</v>
       </c>
-      <c r="C19" s="277" t="str">
+      <c r="C19" s="257" t="str">
         <f>Paėmimas!C19</f>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
@@ -6876,7 +6881,7 @@
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="61"/>
       <c r="B20" s="23"/>
-      <c r="C20" s="278"/>
+      <c r="C20" s="258"/>
       <c r="D20" s="224">
         <f>Paėmimas!L20</f>
         <v>0.05</v>
@@ -6913,7 +6918,7 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="61"/>
       <c r="B21" s="23"/>
-      <c r="C21" s="278"/>
+      <c r="C21" s="258"/>
       <c r="D21" s="224">
         <f>Paėmimas!L21</f>
         <v>0.05</v>
@@ -6950,7 +6955,7 @@
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="61"/>
       <c r="B22" s="23"/>
-      <c r="C22" s="278"/>
+      <c r="C22" s="258"/>
       <c r="D22" s="224">
         <f>Paėmimas!L22</f>
         <v>0.05</v>
@@ -6987,7 +6992,7 @@
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="61"/>
       <c r="B23" s="23"/>
-      <c r="C23" s="278"/>
+      <c r="C23" s="258"/>
       <c r="D23" s="224">
         <f>Paėmimas!L23</f>
         <v>0.05</v>
@@ -7024,7 +7029,7 @@
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="61"/>
       <c r="B24" s="23"/>
-      <c r="C24" s="278"/>
+      <c r="C24" s="258"/>
       <c r="D24" s="224">
         <f>Paėmimas!L24</f>
         <v>0.05</v>
@@ -7061,7 +7066,7 @@
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="61"/>
       <c r="B25" s="23"/>
-      <c r="C25" s="278"/>
+      <c r="C25" s="258"/>
       <c r="D25" s="224">
         <f>Paėmimas!L25</f>
         <v>0.05</v>
@@ -7098,7 +7103,7 @@
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="61"/>
       <c r="B26" s="23"/>
-      <c r="C26" s="278"/>
+      <c r="C26" s="258"/>
       <c r="D26" s="224">
         <f>Paėmimas!L26</f>
         <v>0.05</v>
@@ -7135,7 +7140,7 @@
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="63"/>
       <c r="B27" s="64"/>
-      <c r="C27" s="279"/>
+      <c r="C27" s="259"/>
       <c r="D27" s="224">
         <f>Paėmimas!L27</f>
         <v>0.05</v>
@@ -7293,7 +7298,7 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0" top="0.74803149606299213" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="97" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;CPuslapių &amp;P &amp;R&amp;"Times New Roman,Paryškintasis"E5-5_02         
 2022-02-01, EV</oddFooter>
@@ -7330,10 +7335,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="281" t="s">
+      <c r="C1" s="261" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="281"/>
+      <c r="D1" s="261"/>
       <c r="R1" s="16"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -7586,12 +7591,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="281" t="s">
+      <c r="C1" s="261" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="281"/>
-      <c r="E1" s="281"/>
-      <c r="F1" s="281"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
     </row>
     <row r="2" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="283" t="s">
@@ -7613,49 +7618,49 @@
       <c r="O2" s="283"/>
     </row>
     <row r="4" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="292" t="s">
+      <c r="A4" s="287" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="292" t="s">
+      <c r="B4" s="287" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="289" t="s">
+      <c r="C4" s="298" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="289" t="s">
+      <c r="D4" s="298" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="289" t="s">
+      <c r="E4" s="298" t="s">
         <v>86</v>
       </c>
-      <c r="F4" s="289"/>
-      <c r="G4" s="289"/>
-      <c r="H4" s="289" t="s">
+      <c r="F4" s="298"/>
+      <c r="G4" s="298"/>
+      <c r="H4" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="296" t="s">
+      <c r="I4" s="291" t="s">
         <v>87</v>
       </c>
-      <c r="J4" s="291" t="s">
+      <c r="J4" s="286" t="s">
         <v>88</v>
       </c>
-      <c r="K4" s="291"/>
-      <c r="L4" s="291"/>
-      <c r="M4" s="298" t="s">
+      <c r="K4" s="286"/>
+      <c r="L4" s="286"/>
+      <c r="M4" s="293" t="s">
         <v>89</v>
       </c>
-      <c r="N4" s="291" t="s">
+      <c r="N4" s="286" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="294" t="s">
+      <c r="O4" s="289" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="293"/>
-      <c r="B5" s="293"/>
-      <c r="C5" s="290"/>
-      <c r="D5" s="289"/>
+      <c r="A5" s="288"/>
+      <c r="B5" s="288"/>
+      <c r="C5" s="299"/>
+      <c r="D5" s="298"/>
       <c r="E5" s="120">
         <v>1</v>
       </c>
@@ -7665,8 +7670,8 @@
       <c r="G5" s="120">
         <v>3</v>
       </c>
-      <c r="H5" s="289"/>
-      <c r="I5" s="297"/>
+      <c r="H5" s="298"/>
+      <c r="I5" s="292"/>
       <c r="J5" s="12">
         <v>1</v>
       </c>
@@ -7676,16 +7681,16 @@
       <c r="L5" s="12">
         <v>3</v>
       </c>
-      <c r="M5" s="299"/>
-      <c r="N5" s="291"/>
-      <c r="O5" s="295"/>
+      <c r="M5" s="294"/>
+      <c r="N5" s="286"/>
+      <c r="O5" s="290"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="251">
         <f>Paėmimas!B6</f>
         <v>1</v>
       </c>
-      <c r="B6" s="286" t="str">
+      <c r="B6" s="295" t="str">
         <f>Paėmimas!C6</f>
         <v>UAB ,,Ekopartneris", L. Ivinskio g. 65, Kaunas. Katilinė. Taršos šaltinis  Nr. 001.</v>
       </c>
@@ -7735,7 +7740,7 @@
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34"/>
-      <c r="B7" s="287"/>
+      <c r="B7" s="296"/>
       <c r="C7" s="33">
         <v>2</v>
       </c>
@@ -7772,7 +7777,7 @@
     </row>
     <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34"/>
-      <c r="B8" s="287"/>
+      <c r="B8" s="296"/>
       <c r="C8" s="33"/>
       <c r="D8" s="92"/>
       <c r="E8" s="201"/>
@@ -7792,7 +7797,7 @@
     </row>
     <row r="9" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A9" s="34"/>
-      <c r="B9" s="287"/>
+      <c r="B9" s="296"/>
       <c r="C9" s="33">
         <v>3</v>
       </c>
@@ -7829,7 +7834,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="34"/>
-      <c r="B10" s="287"/>
+      <c r="B10" s="296"/>
       <c r="C10" s="33"/>
       <c r="D10" s="92"/>
       <c r="E10" s="201"/>
@@ -7846,7 +7851,7 @@
     </row>
     <row r="11" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A11" s="34"/>
-      <c r="B11" s="287"/>
+      <c r="B11" s="296"/>
       <c r="C11" s="33">
         <v>41</v>
       </c>
@@ -7882,7 +7887,7 @@
     </row>
     <row r="12" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="34"/>
-      <c r="B12" s="287"/>
+      <c r="B12" s="296"/>
       <c r="C12" s="115" t="s">
         <v>46</v>
       </c>
@@ -7918,7 +7923,7 @@
     </row>
     <row r="13" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A13" s="34"/>
-      <c r="B13" s="287"/>
+      <c r="B13" s="296"/>
       <c r="C13" s="116" t="s">
         <v>47</v>
       </c>
@@ -7954,7 +7959,7 @@
     </row>
     <row r="14" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A14" s="34"/>
-      <c r="B14" s="287"/>
+      <c r="B14" s="296"/>
       <c r="C14" s="116" t="s">
         <v>48</v>
       </c>
@@ -7990,7 +7995,7 @@
     </row>
     <row r="15" spans="1:16" ht="17" x14ac:dyDescent="0.45">
       <c r="A15" s="34"/>
-      <c r="B15" s="287"/>
+      <c r="B15" s="296"/>
       <c r="C15" s="117" t="s">
         <v>49</v>
       </c>
@@ -8026,7 +8031,7 @@
     </row>
     <row r="16" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="22"/>
-      <c r="B16" s="288"/>
+      <c r="B16" s="297"/>
       <c r="C16" s="33"/>
       <c r="D16" s="95"/>
       <c r="E16" s="21"/>
@@ -8060,6 +8065,11 @@
     </sortState>
   </autoFilter>
   <mergeCells count="14">
+    <mergeCell ref="B6:B16"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:H5"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A2:O2"/>
@@ -8069,11 +8079,6 @@
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="B6:B16"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:H5"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -8149,6 +8154,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
     <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
@@ -8403,28 +8428,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A76AEC4-30EA-47BC-874D-3E7B98533503}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709F4DDD-DF1A-450D-8BF1-976CA47CFD58}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8436,12 +8448,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709F4DDD-DF1A-450D-8BF1-976CA47CFD58}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A76AEC4-30EA-47BC-874D-3E7B98533503}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
     <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Ivestis2.xlsx
+++ b/Ivestis2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="Šios_darbaknygės" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agentura2020.sharepoint.com/sites/VidurioLietuvosaplinkostyrimuskyrius/Bendrai naudojami dokumentai/EB7-014 Darbuotojų failai/Tomo/Python 3.14.3/Skaiciavimai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{D8ED3FA4-1188-4E70-924F-660A50F19C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95D2F3A6-D36A-4B1D-863B-1FF9AD1318ED}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="13_ncr:1_{D8ED3FA4-1188-4E70-924F-660A50F19C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C12CB74-2836-4FC7-B198-2453F28E0752}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="3" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="821" firstSheet="1" activeTab="4" xr2:uid="{B097D0E3-85A4-46F7-964F-ABE00A6941B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Compatibility Report" sheetId="4" state="hidden" r:id="rId1"/>
@@ -4396,7 +4396,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YnNuFyjIZWP4o8siiNLOxJuXYMQvqdvZ9OrGGKpnMs1jyahS3pGpSVhE713S/7NZQvFDz0ZfCGMwTjhjC08CdQ==" saltValue="gCAgvRWICbIOkCsyhMCWFQ==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="11">
     <mergeCell ref="AB20:AB21"/>
     <mergeCell ref="D2:Z2"/>
@@ -6604,7 +6604,7 @@
       <c r="J30" s="96"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Q7zQYUs0oFV/Gufx4DvoPWUpCjgOT2OzgA8jP4+OReQfg8sPFVBJlJin6okpsn/bA60CDJSSySZP7yIIZexC0Q==" saltValue="I0m09WVlXZjQAlrY7KWzKQ==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="4">
     <mergeCell ref="C2:M2"/>
     <mergeCell ref="C1:D1"/>
@@ -7696,15 +7696,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1A676EA-343E-4342-8BA5-7010E1EF44D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1A676EA-343E-4342-8BA5-7010E1EF44D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709F4DDD-DF1A-450D-8BF1-976CA47CFD58}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
     <ds:schemaRef ds:uri="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
